--- a/Deviation.xlsx
+++ b/Deviation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8E90A6-D013-4B90-B69E-88BAF2A6AADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4F5876-674E-4A2E-83A8-5A66E85AF2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$K$369</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$N$369</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3323" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3747" uniqueCount="111">
   <si>
     <t>District</t>
   </si>
@@ -306,9 +306,6 @@
     <t>ALL  MATERIALS  PLACED AS CALLED FOR BY APPROVED DESIGN AND APPROVED STC SPECIFICATIONS?</t>
   </si>
   <si>
-    <t>2521001663</t>
-  </si>
-  <si>
     <t>Rejected deviation approved by Regional supervisor</t>
   </si>
   <si>
@@ -324,37 +321,52 @@
     <t>ARE THE CABLES ROUTED AND RACKED CORRECTLY IN EACH MANHOLE / HANDHOLE?</t>
   </si>
   <si>
-    <t>2521001669</t>
-  </si>
-  <si>
-    <t>2521001668</t>
-  </si>
-  <si>
-    <t>2521001662</t>
-  </si>
-  <si>
-    <t>2521001661</t>
-  </si>
-  <si>
     <t>THE ASPHALT / CONCRETE WAS PROVIDED BY STC APPROVED SUPPLIER?</t>
   </si>
   <si>
     <t>BADGE ID NOT CORRESPONDING TO WORKER</t>
   </si>
   <si>
-    <t>2512000178</t>
-  </si>
-  <si>
     <t>CONTRACTOR MARKED THE TRENCH PATH AS PER THE DESIGN BEFORE START TRENCHING ?</t>
   </si>
   <si>
-    <t>2512000177</t>
+    <t>RIYADH</t>
   </si>
   <si>
-    <t>2512000176</t>
+    <t>Inspector</t>
   </si>
   <si>
-    <t>RIYADH</t>
+    <t>Civil Foreman</t>
+  </si>
+  <si>
+    <t>Expected Penalties</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>لياقت</t>
+  </si>
+  <si>
+    <t>محمد على</t>
+  </si>
+  <si>
+    <t>ياسر عبد الرحمن</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>طارق عمار</t>
+  </si>
+  <si>
+    <t>اسلام عبد القوي</t>
+  </si>
+  <si>
+    <t>مقاول باطن / تابع لمهند</t>
+  </si>
+  <si>
+    <t>مهند</t>
   </si>
 </sst>
 </file>
@@ -364,10 +376,15 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -390,9 +407,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -707,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8344894E-F246-4BB9-9C9B-CB684317BD40}">
-  <dimension ref="A1:K369"/>
+  <dimension ref="A1:N369"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
@@ -717,9 +735,10 @@
     <col min="7" max="7" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.44140625" customWidth="1"/>
     <col min="9" max="9" width="13.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -753,13 +772,22 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>73</v>
       </c>
-      <c r="B2" t="s">
-        <v>96</v>
+      <c r="B2">
+        <v>2521001669</v>
       </c>
       <c r="C2" t="s">
         <v>39</v>
@@ -788,13 +816,19 @@
       <c r="K2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" t="s">
+        <v>103</v>
+      </c>
+      <c r="M2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
-      <c r="B3" t="s">
-        <v>96</v>
+      <c r="B3">
+        <v>2521001669</v>
       </c>
       <c r="C3" t="s">
         <v>49</v>
@@ -823,13 +857,19 @@
       <c r="K3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" t="s">
+        <v>103</v>
+      </c>
+      <c r="M3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>73</v>
       </c>
-      <c r="B4" t="s">
-        <v>96</v>
+      <c r="B4">
+        <v>2521001669</v>
       </c>
       <c r="C4" t="s">
         <v>80</v>
@@ -858,13 +898,19 @@
       <c r="K4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4" t="s">
+        <v>103</v>
+      </c>
+      <c r="M4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>73</v>
       </c>
-      <c r="B5" t="s">
-        <v>96</v>
+      <c r="B5">
+        <v>2521001669</v>
       </c>
       <c r="C5" t="s">
         <v>45</v>
@@ -893,13 +939,19 @@
       <c r="K5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>73</v>
       </c>
-      <c r="B6" t="s">
-        <v>96</v>
+      <c r="B6">
+        <v>2521001669</v>
       </c>
       <c r="C6" t="s">
         <v>59</v>
@@ -928,13 +980,19 @@
       <c r="K6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6" t="s">
+        <v>103</v>
+      </c>
+      <c r="M6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>73</v>
       </c>
-      <c r="B7" t="s">
-        <v>96</v>
+      <c r="B7">
+        <v>2521001669</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
@@ -963,13 +1021,19 @@
       <c r="K7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" t="s">
+        <v>103</v>
+      </c>
+      <c r="M7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>73</v>
       </c>
-      <c r="B8" t="s">
-        <v>96</v>
+      <c r="B8">
+        <v>2521001669</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
@@ -998,13 +1062,19 @@
       <c r="K8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8" t="s">
+        <v>103</v>
+      </c>
+      <c r="M8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>73</v>
       </c>
-      <c r="B9" t="s">
-        <v>96</v>
+      <c r="B9">
+        <v>2521001669</v>
       </c>
       <c r="C9" t="s">
         <v>80</v>
@@ -1033,13 +1103,19 @@
       <c r="K9" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9" t="s">
+        <v>103</v>
+      </c>
+      <c r="M9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>73</v>
       </c>
-      <c r="B10" t="s">
-        <v>96</v>
+      <c r="B10">
+        <v>2521001669</v>
       </c>
       <c r="C10" t="s">
         <v>59</v>
@@ -1068,13 +1144,19 @@
       <c r="K10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10" t="s">
+        <v>103</v>
+      </c>
+      <c r="M10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>73</v>
       </c>
-      <c r="B11" t="s">
-        <v>96</v>
+      <c r="B11">
+        <v>2521001669</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
@@ -1103,13 +1185,19 @@
       <c r="K11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11" t="s">
+        <v>103</v>
+      </c>
+      <c r="M11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>73</v>
       </c>
-      <c r="B12" t="s">
-        <v>96</v>
+      <c r="B12">
+        <v>2521001669</v>
       </c>
       <c r="C12" t="s">
         <v>45</v>
@@ -1138,13 +1226,19 @@
       <c r="K12" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>73</v>
       </c>
-      <c r="B13" t="s">
-        <v>96</v>
+      <c r="B13">
+        <v>2521001669</v>
       </c>
       <c r="C13" t="s">
         <v>75</v>
@@ -1173,13 +1267,19 @@
       <c r="K13" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13" t="s">
+        <v>103</v>
+      </c>
+      <c r="M13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>73</v>
       </c>
-      <c r="B14" t="s">
-        <v>96</v>
+      <c r="B14">
+        <v>2521001669</v>
       </c>
       <c r="C14" t="s">
         <v>42</v>
@@ -1208,13 +1308,19 @@
       <c r="K14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14" t="s">
+        <v>103</v>
+      </c>
+      <c r="M14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>73</v>
       </c>
-      <c r="B15" t="s">
-        <v>96</v>
+      <c r="B15">
+        <v>2521001669</v>
       </c>
       <c r="C15" t="s">
         <v>37</v>
@@ -1243,13 +1349,19 @@
       <c r="K15" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>73</v>
       </c>
-      <c r="B16" t="s">
-        <v>96</v>
+      <c r="B16">
+        <v>2521001669</v>
       </c>
       <c r="C16" t="s">
         <v>68</v>
@@ -1278,13 +1390,19 @@
       <c r="K16" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16" t="s">
+        <v>103</v>
+      </c>
+      <c r="M16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>73</v>
       </c>
-      <c r="B17" t="s">
-        <v>96</v>
+      <c r="B17">
+        <v>2521001669</v>
       </c>
       <c r="C17" t="s">
         <v>49</v>
@@ -1313,13 +1431,19 @@
       <c r="K17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17" t="s">
+        <v>103</v>
+      </c>
+      <c r="M17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>73</v>
       </c>
-      <c r="B18" t="s">
-        <v>96</v>
+      <c r="B18">
+        <v>2521001669</v>
       </c>
       <c r="C18" t="s">
         <v>76</v>
@@ -1348,13 +1472,19 @@
       <c r="K18" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18" t="s">
+        <v>103</v>
+      </c>
+      <c r="M18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>73</v>
       </c>
-      <c r="B19" t="s">
-        <v>96</v>
+      <c r="B19">
+        <v>2521001669</v>
       </c>
       <c r="C19" t="s">
         <v>49</v>
@@ -1383,13 +1513,19 @@
       <c r="K19" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19" t="s">
+        <v>103</v>
+      </c>
+      <c r="M19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>73</v>
       </c>
-      <c r="B20" t="s">
-        <v>96</v>
+      <c r="B20">
+        <v>2521001669</v>
       </c>
       <c r="C20" t="s">
         <v>39</v>
@@ -1418,13 +1554,19 @@
       <c r="K20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20" t="s">
+        <v>103</v>
+      </c>
+      <c r="M20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>73</v>
       </c>
-      <c r="B21" t="s">
-        <v>96</v>
+      <c r="B21">
+        <v>2521001669</v>
       </c>
       <c r="C21" t="s">
         <v>74</v>
@@ -1453,13 +1595,19 @@
       <c r="K21" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21" t="s">
+        <v>103</v>
+      </c>
+      <c r="M21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
-      <c r="B22" t="s">
-        <v>96</v>
+      <c r="B22">
+        <v>2521001669</v>
       </c>
       <c r="C22" t="s">
         <v>42</v>
@@ -1488,13 +1636,19 @@
       <c r="K22" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22" t="s">
+        <v>103</v>
+      </c>
+      <c r="M22" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>73</v>
       </c>
-      <c r="B23" t="s">
-        <v>96</v>
+      <c r="B23">
+        <v>2521001669</v>
       </c>
       <c r="C23" t="s">
         <v>81</v>
@@ -1523,13 +1677,19 @@
       <c r="K23" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23" t="s">
+        <v>103</v>
+      </c>
+      <c r="M23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>73</v>
       </c>
-      <c r="B24" t="s">
-        <v>96</v>
+      <c r="B24">
+        <v>2521001669</v>
       </c>
       <c r="C24" t="s">
         <v>68</v>
@@ -1558,13 +1718,19 @@
       <c r="K24" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24" t="s">
+        <v>103</v>
+      </c>
+      <c r="M24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>73</v>
       </c>
-      <c r="B25" t="s">
-        <v>96</v>
+      <c r="B25">
+        <v>2521001669</v>
       </c>
       <c r="C25" t="s">
         <v>86</v>
@@ -1593,13 +1759,19 @@
       <c r="K25" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25" t="s">
+        <v>103</v>
+      </c>
+      <c r="M25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>73</v>
       </c>
-      <c r="B26" t="s">
-        <v>96</v>
+      <c r="B26">
+        <v>2521001669</v>
       </c>
       <c r="C26" t="s">
         <v>48</v>
@@ -1628,13 +1800,22 @@
       <c r="K26" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26" t="s">
+        <v>103</v>
+      </c>
+      <c r="M26" t="s">
+        <v>104</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>73</v>
       </c>
-      <c r="B27" t="s">
-        <v>96</v>
+      <c r="B27">
+        <v>2521001669</v>
       </c>
       <c r="C27" t="s">
         <v>52</v>
@@ -1663,13 +1844,22 @@
       <c r="K27" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27" t="s">
+        <v>103</v>
+      </c>
+      <c r="M27" t="s">
+        <v>104</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>73</v>
       </c>
-      <c r="B28" t="s">
-        <v>96</v>
+      <c r="B28">
+        <v>2521001669</v>
       </c>
       <c r="C28" t="s">
         <v>28</v>
@@ -1698,13 +1888,19 @@
       <c r="K28" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28" t="s">
+        <v>103</v>
+      </c>
+      <c r="M28" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>73</v>
       </c>
-      <c r="B29" t="s">
-        <v>96</v>
+      <c r="B29">
+        <v>2521001669</v>
       </c>
       <c r="C29" t="s">
         <v>35</v>
@@ -1733,13 +1929,19 @@
       <c r="K29" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29" t="s">
+        <v>103</v>
+      </c>
+      <c r="M29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>73</v>
       </c>
-      <c r="B30" t="s">
-        <v>96</v>
+      <c r="B30">
+        <v>2521001669</v>
       </c>
       <c r="C30" t="s">
         <v>49</v>
@@ -1768,13 +1970,19 @@
       <c r="K30" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30" t="s">
+        <v>103</v>
+      </c>
+      <c r="M30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>73</v>
       </c>
-      <c r="B31" t="s">
-        <v>96</v>
+      <c r="B31">
+        <v>2521001669</v>
       </c>
       <c r="C31" t="s">
         <v>48</v>
@@ -1803,13 +2011,19 @@
       <c r="K31" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31" t="s">
+        <v>103</v>
+      </c>
+      <c r="M31" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>73</v>
       </c>
-      <c r="B32" t="s">
-        <v>96</v>
+      <c r="B32">
+        <v>2521001669</v>
       </c>
       <c r="C32" t="s">
         <v>76</v>
@@ -1838,13 +2052,19 @@
       <c r="K32" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32" t="s">
+        <v>103</v>
+      </c>
+      <c r="M32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>73</v>
       </c>
-      <c r="B33" t="s">
-        <v>96</v>
+      <c r="B33">
+        <v>2521001669</v>
       </c>
       <c r="C33" t="s">
         <v>49</v>
@@ -1873,13 +2093,19 @@
       <c r="K33" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33" t="s">
+        <v>103</v>
+      </c>
+      <c r="M33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>73</v>
       </c>
-      <c r="B34" t="s">
-        <v>96</v>
+      <c r="B34">
+        <v>2521001669</v>
       </c>
       <c r="C34" t="s">
         <v>37</v>
@@ -1908,13 +2134,19 @@
       <c r="K34" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34" t="s">
+        <v>103</v>
+      </c>
+      <c r="M34" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>73</v>
       </c>
-      <c r="B35" t="s">
-        <v>96</v>
+      <c r="B35">
+        <v>2521001669</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -1943,13 +2175,19 @@
       <c r="K35" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35" t="s">
+        <v>103</v>
+      </c>
+      <c r="M35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
-      <c r="B36" t="s">
-        <v>96</v>
+      <c r="B36">
+        <v>2521001669</v>
       </c>
       <c r="C36" t="s">
         <v>68</v>
@@ -1978,13 +2216,19 @@
       <c r="K36" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36" t="s">
+        <v>103</v>
+      </c>
+      <c r="M36" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>73</v>
       </c>
-      <c r="B37" t="s">
-        <v>96</v>
+      <c r="B37">
+        <v>2521001669</v>
       </c>
       <c r="C37" t="s">
         <v>49</v>
@@ -2013,13 +2257,19 @@
       <c r="K37" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37" t="s">
+        <v>103</v>
+      </c>
+      <c r="M37" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>73</v>
       </c>
-      <c r="B38" t="s">
-        <v>96</v>
+      <c r="B38">
+        <v>2521001669</v>
       </c>
       <c r="C38" t="s">
         <v>48</v>
@@ -2048,13 +2298,19 @@
       <c r="K38" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38" t="s">
+        <v>103</v>
+      </c>
+      <c r="M38" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>73</v>
       </c>
-      <c r="B39" t="s">
-        <v>96</v>
+      <c r="B39">
+        <v>2521001669</v>
       </c>
       <c r="C39" t="s">
         <v>80</v>
@@ -2083,13 +2339,19 @@
       <c r="K39" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39" t="s">
+        <v>103</v>
+      </c>
+      <c r="M39" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>73</v>
       </c>
-      <c r="B40" t="s">
-        <v>96</v>
+      <c r="B40">
+        <v>2521001669</v>
       </c>
       <c r="C40" t="s">
         <v>49</v>
@@ -2118,13 +2380,19 @@
       <c r="K40" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40" t="s">
+        <v>103</v>
+      </c>
+      <c r="M40" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>73</v>
       </c>
-      <c r="B41" t="s">
-        <v>96</v>
+      <c r="B41">
+        <v>2521001669</v>
       </c>
       <c r="C41" t="s">
         <v>39</v>
@@ -2153,13 +2421,19 @@
       <c r="K41" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41" t="s">
+        <v>103</v>
+      </c>
+      <c r="M41" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>73</v>
       </c>
-      <c r="B42" t="s">
-        <v>96</v>
+      <c r="B42">
+        <v>2521001669</v>
       </c>
       <c r="C42" t="s">
         <v>48</v>
@@ -2188,13 +2462,19 @@
       <c r="K42" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42" t="s">
+        <v>103</v>
+      </c>
+      <c r="M42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>73</v>
       </c>
-      <c r="B43" t="s">
-        <v>96</v>
+      <c r="B43">
+        <v>2521001669</v>
       </c>
       <c r="C43" t="s">
         <v>49</v>
@@ -2223,13 +2503,19 @@
       <c r="K43" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43" t="s">
+        <v>103</v>
+      </c>
+      <c r="M43" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>73</v>
       </c>
-      <c r="B44" t="s">
-        <v>96</v>
+      <c r="B44">
+        <v>2521001669</v>
       </c>
       <c r="C44" t="s">
         <v>69</v>
@@ -2258,13 +2544,19 @@
       <c r="K44" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L44" t="s">
+        <v>103</v>
+      </c>
+      <c r="M44" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>73</v>
       </c>
-      <c r="B45" t="s">
-        <v>96</v>
+      <c r="B45">
+        <v>2521001669</v>
       </c>
       <c r="C45" t="s">
         <v>28</v>
@@ -2293,13 +2585,19 @@
       <c r="K45" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L45" t="s">
+        <v>103</v>
+      </c>
+      <c r="M45" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>73</v>
       </c>
-      <c r="B46" t="s">
-        <v>96</v>
+      <c r="B46">
+        <v>2521001669</v>
       </c>
       <c r="C46" t="s">
         <v>35</v>
@@ -2328,13 +2626,19 @@
       <c r="K46" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46" t="s">
+        <v>103</v>
+      </c>
+      <c r="M46" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>73</v>
       </c>
-      <c r="B47" t="s">
-        <v>96</v>
+      <c r="B47">
+        <v>2521001669</v>
       </c>
       <c r="C47" t="s">
         <v>79</v>
@@ -2363,13 +2667,19 @@
       <c r="K47" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L47" t="s">
+        <v>103</v>
+      </c>
+      <c r="M47" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>73</v>
       </c>
-      <c r="B48" t="s">
-        <v>96</v>
+      <c r="B48">
+        <v>2521001669</v>
       </c>
       <c r="C48" t="s">
         <v>81</v>
@@ -2398,13 +2708,19 @@
       <c r="K48" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48" t="s">
+        <v>103</v>
+      </c>
+      <c r="M48" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>73</v>
       </c>
-      <c r="B49" t="s">
-        <v>96</v>
+      <c r="B49">
+        <v>2521001669</v>
       </c>
       <c r="C49" t="s">
         <v>37</v>
@@ -2433,13 +2749,19 @@
       <c r="K49" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49" t="s">
+        <v>103</v>
+      </c>
+      <c r="M49" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>73</v>
       </c>
-      <c r="B50" t="s">
-        <v>96</v>
+      <c r="B50">
+        <v>2521001669</v>
       </c>
       <c r="C50" t="s">
         <v>49</v>
@@ -2468,13 +2790,19 @@
       <c r="K50" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L50" t="s">
+        <v>103</v>
+      </c>
+      <c r="M50" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>73</v>
       </c>
-      <c r="B51" t="s">
-        <v>96</v>
+      <c r="B51">
+        <v>2521001669</v>
       </c>
       <c r="C51" t="s">
         <v>69</v>
@@ -2503,13 +2831,19 @@
       <c r="K51" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L51" t="s">
+        <v>103</v>
+      </c>
+      <c r="M51" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>73</v>
       </c>
-      <c r="B52" t="s">
-        <v>96</v>
+      <c r="B52">
+        <v>2521001669</v>
       </c>
       <c r="C52" t="s">
         <v>59</v>
@@ -2538,13 +2872,19 @@
       <c r="K52" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L52" t="s">
+        <v>103</v>
+      </c>
+      <c r="M52" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>73</v>
       </c>
-      <c r="B53" t="s">
-        <v>96</v>
+      <c r="B53">
+        <v>2521001669</v>
       </c>
       <c r="C53" t="s">
         <v>76</v>
@@ -2573,13 +2913,19 @@
       <c r="K53" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L53" t="s">
+        <v>103</v>
+      </c>
+      <c r="M53" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>73</v>
       </c>
-      <c r="B54" t="s">
-        <v>96</v>
+      <c r="B54">
+        <v>2521001669</v>
       </c>
       <c r="C54" t="s">
         <v>48</v>
@@ -2608,13 +2954,19 @@
       <c r="K54" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L54" t="s">
+        <v>103</v>
+      </c>
+      <c r="M54" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>73</v>
       </c>
-      <c r="B55" t="s">
-        <v>96</v>
+      <c r="B55">
+        <v>2521001669</v>
       </c>
       <c r="C55" t="s">
         <v>49</v>
@@ -2643,13 +2995,19 @@
       <c r="K55" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L55" t="s">
+        <v>103</v>
+      </c>
+      <c r="M55" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>73</v>
       </c>
-      <c r="B56" t="s">
-        <v>96</v>
+      <c r="B56">
+        <v>2521001669</v>
       </c>
       <c r="C56" t="s">
         <v>76</v>
@@ -2678,13 +3036,19 @@
       <c r="K56" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L56" t="s">
+        <v>103</v>
+      </c>
+      <c r="M56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>73</v>
       </c>
-      <c r="B57" t="s">
-        <v>96</v>
+      <c r="B57">
+        <v>2521001669</v>
       </c>
       <c r="C57" t="s">
         <v>49</v>
@@ -2713,13 +3077,19 @@
       <c r="K57" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L57" t="s">
+        <v>103</v>
+      </c>
+      <c r="M57" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>73</v>
       </c>
-      <c r="B58" t="s">
-        <v>96</v>
+      <c r="B58">
+        <v>2521001669</v>
       </c>
       <c r="C58" t="s">
         <v>69</v>
@@ -2748,13 +3118,19 @@
       <c r="K58" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L58" t="s">
+        <v>103</v>
+      </c>
+      <c r="M58" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>73</v>
       </c>
-      <c r="B59" t="s">
-        <v>96</v>
+      <c r="B59">
+        <v>2521001669</v>
       </c>
       <c r="C59" t="s">
         <v>28</v>
@@ -2783,13 +3159,19 @@
       <c r="K59" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L59" t="s">
+        <v>103</v>
+      </c>
+      <c r="M59" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>73</v>
       </c>
-      <c r="B60" t="s">
-        <v>96</v>
+      <c r="B60">
+        <v>2521001669</v>
       </c>
       <c r="C60" t="s">
         <v>28</v>
@@ -2818,13 +3200,19 @@
       <c r="K60" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L60" t="s">
+        <v>103</v>
+      </c>
+      <c r="M60" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>73</v>
       </c>
-      <c r="B61" t="s">
-        <v>96</v>
+      <c r="B61">
+        <v>2521001669</v>
       </c>
       <c r="C61" t="s">
         <v>49</v>
@@ -2853,13 +3241,19 @@
       <c r="K61" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L61" t="s">
+        <v>103</v>
+      </c>
+      <c r="M61" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>73</v>
       </c>
-      <c r="B62" t="s">
-        <v>96</v>
+      <c r="B62">
+        <v>2521001669</v>
       </c>
       <c r="C62" t="s">
         <v>45</v>
@@ -2888,13 +3282,19 @@
       <c r="K62" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L62" t="s">
+        <v>103</v>
+      </c>
+      <c r="M62" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>73</v>
       </c>
-      <c r="B63" t="s">
-        <v>96</v>
+      <c r="B63">
+        <v>2521001669</v>
       </c>
       <c r="C63" t="s">
         <v>42</v>
@@ -2923,13 +3323,19 @@
       <c r="K63" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L63" t="s">
+        <v>103</v>
+      </c>
+      <c r="M63" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>73</v>
       </c>
-      <c r="B64" t="s">
-        <v>96</v>
+      <c r="B64">
+        <v>2521001669</v>
       </c>
       <c r="C64" t="s">
         <v>49</v>
@@ -2958,13 +3364,19 @@
       <c r="K64" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L64" t="s">
+        <v>103</v>
+      </c>
+      <c r="M64" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>73</v>
       </c>
-      <c r="B65" t="s">
-        <v>96</v>
+      <c r="B65">
+        <v>2521001669</v>
       </c>
       <c r="C65" t="s">
         <v>80</v>
@@ -2993,13 +3405,19 @@
       <c r="K65" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L65" t="s">
+        <v>103</v>
+      </c>
+      <c r="M65" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>73</v>
       </c>
-      <c r="B66" t="s">
-        <v>96</v>
+      <c r="B66">
+        <v>2521001669</v>
       </c>
       <c r="C66" t="s">
         <v>60</v>
@@ -3028,13 +3446,19 @@
       <c r="K66" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L66" t="s">
+        <v>103</v>
+      </c>
+      <c r="M66" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>73</v>
       </c>
-      <c r="B67" t="s">
-        <v>96</v>
+      <c r="B67">
+        <v>2521001669</v>
       </c>
       <c r="C67" t="s">
         <v>34</v>
@@ -3063,13 +3487,19 @@
       <c r="K67" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L67" t="s">
+        <v>103</v>
+      </c>
+      <c r="M67" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>73</v>
       </c>
-      <c r="B68" t="s">
-        <v>96</v>
+      <c r="B68">
+        <v>2521001669</v>
       </c>
       <c r="C68" t="s">
         <v>50</v>
@@ -3098,13 +3528,19 @@
       <c r="K68" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L68" t="s">
+        <v>103</v>
+      </c>
+      <c r="M68" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>73</v>
       </c>
-      <c r="B69" t="s">
-        <v>96</v>
+      <c r="B69">
+        <v>2521001669</v>
       </c>
       <c r="C69" t="s">
         <v>65</v>
@@ -3133,13 +3569,19 @@
       <c r="K69" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L69" t="s">
+        <v>103</v>
+      </c>
+      <c r="M69" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>73</v>
       </c>
-      <c r="B70" t="s">
-        <v>96</v>
+      <c r="B70">
+        <v>2521001669</v>
       </c>
       <c r="C70" t="s">
         <v>28</v>
@@ -3168,13 +3610,19 @@
       <c r="K70" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L70" t="s">
+        <v>103</v>
+      </c>
+      <c r="M70" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>73</v>
       </c>
-      <c r="B71" t="s">
-        <v>96</v>
+      <c r="B71">
+        <v>2521001669</v>
       </c>
       <c r="C71" t="s">
         <v>60</v>
@@ -3203,13 +3651,19 @@
       <c r="K71" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L71" t="s">
+        <v>103</v>
+      </c>
+      <c r="M71" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>73</v>
       </c>
-      <c r="B72" t="s">
-        <v>96</v>
+      <c r="B72">
+        <v>2521001669</v>
       </c>
       <c r="C72" t="s">
         <v>80</v>
@@ -3238,13 +3692,19 @@
       <c r="K72" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L72" t="s">
+        <v>103</v>
+      </c>
+      <c r="M72" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>73</v>
       </c>
-      <c r="B73" t="s">
-        <v>96</v>
+      <c r="B73">
+        <v>2521001669</v>
       </c>
       <c r="C73" t="s">
         <v>53</v>
@@ -3273,13 +3733,19 @@
       <c r="K73" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L73" t="s">
+        <v>103</v>
+      </c>
+      <c r="M73" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
-        <v>96</v>
+      <c r="B74">
+        <v>2521001669</v>
       </c>
       <c r="C74" t="s">
         <v>30</v>
@@ -3308,16 +3774,22 @@
       <c r="K74" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L74" t="s">
+        <v>103</v>
+      </c>
+      <c r="M74" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>73</v>
       </c>
-      <c r="B75" t="s">
-        <v>96</v>
+      <c r="B75">
+        <v>2521001669</v>
       </c>
       <c r="C75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D75">
         <v>72</v>
@@ -3343,13 +3815,19 @@
       <c r="K75" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L75" t="s">
+        <v>103</v>
+      </c>
+      <c r="M75" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>73</v>
       </c>
-      <c r="B76" t="s">
-        <v>96</v>
+      <c r="B76">
+        <v>2521001669</v>
       </c>
       <c r="C76" t="s">
         <v>34</v>
@@ -3378,16 +3856,22 @@
       <c r="K76" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L76" t="s">
+        <v>103</v>
+      </c>
+      <c r="M76" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>73</v>
       </c>
-      <c r="B77" t="s">
-        <v>96</v>
+      <c r="B77">
+        <v>2521001669</v>
       </c>
       <c r="C77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D77">
         <v>72</v>
@@ -3413,13 +3897,19 @@
       <c r="K77" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L77" t="s">
+        <v>103</v>
+      </c>
+      <c r="M77" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>73</v>
       </c>
-      <c r="B78" t="s">
-        <v>90</v>
+      <c r="B78">
+        <v>2521001663</v>
       </c>
       <c r="C78" t="s">
         <v>12</v>
@@ -3448,13 +3938,19 @@
       <c r="K78" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L78" t="s">
+        <v>105</v>
+      </c>
+      <c r="M78" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>73</v>
       </c>
-      <c r="B79" t="s">
-        <v>90</v>
+      <c r="B79">
+        <v>2521001663</v>
       </c>
       <c r="C79" t="s">
         <v>48</v>
@@ -3483,13 +3979,19 @@
       <c r="K79" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L79" t="s">
+        <v>105</v>
+      </c>
+      <c r="M79" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>73</v>
       </c>
-      <c r="B80" t="s">
-        <v>90</v>
+      <c r="B80">
+        <v>2521001663</v>
       </c>
       <c r="C80" t="s">
         <v>48</v>
@@ -3518,13 +4020,19 @@
       <c r="K80" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L80" t="s">
+        <v>105</v>
+      </c>
+      <c r="M80" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>73</v>
       </c>
-      <c r="B81" t="s">
-        <v>90</v>
+      <c r="B81">
+        <v>2521001663</v>
       </c>
       <c r="C81" t="s">
         <v>48</v>
@@ -3553,13 +4061,19 @@
       <c r="K81" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L81" t="s">
+        <v>105</v>
+      </c>
+      <c r="M81" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>73</v>
       </c>
-      <c r="B82" t="s">
-        <v>90</v>
+      <c r="B82">
+        <v>2521001663</v>
       </c>
       <c r="C82" t="s">
         <v>28</v>
@@ -3588,13 +4102,19 @@
       <c r="K82" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L82" t="s">
+        <v>105</v>
+      </c>
+      <c r="M82" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>73</v>
       </c>
-      <c r="B83" t="s">
-        <v>90</v>
+      <c r="B83">
+        <v>2521001663</v>
       </c>
       <c r="C83" t="s">
         <v>28</v>
@@ -3623,13 +4143,19 @@
       <c r="K83" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L83" t="s">
+        <v>105</v>
+      </c>
+      <c r="M83" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>73</v>
       </c>
-      <c r="B84" t="s">
-        <v>90</v>
+      <c r="B84">
+        <v>2521001663</v>
       </c>
       <c r="C84" t="s">
         <v>75</v>
@@ -3641,7 +4167,7 @@
         <v>20</v>
       </c>
       <c r="F84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G84" s="1">
         <v>46043.63178541667</v>
@@ -3658,13 +4184,19 @@
       <c r="K84" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L84" t="s">
+        <v>105</v>
+      </c>
+      <c r="M84" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>73</v>
       </c>
-      <c r="B85" t="s">
-        <v>90</v>
+      <c r="B85">
+        <v>2521001663</v>
       </c>
       <c r="C85" t="s">
         <v>49</v>
@@ -3693,13 +4225,19 @@
       <c r="K85" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L85" t="s">
+        <v>105</v>
+      </c>
+      <c r="M85" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>73</v>
       </c>
-      <c r="B86" t="s">
-        <v>90</v>
+      <c r="B86">
+        <v>2521001663</v>
       </c>
       <c r="C86" t="s">
         <v>88</v>
@@ -3728,13 +4266,19 @@
       <c r="K86" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L86" t="s">
+        <v>105</v>
+      </c>
+      <c r="M86" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>73</v>
       </c>
-      <c r="B87" t="s">
-        <v>90</v>
+      <c r="B87">
+        <v>2521001663</v>
       </c>
       <c r="C87" t="s">
         <v>45</v>
@@ -3763,13 +4307,19 @@
       <c r="K87" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L87" t="s">
+        <v>105</v>
+      </c>
+      <c r="M87" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>73</v>
       </c>
-      <c r="B88" t="s">
-        <v>90</v>
+      <c r="B88">
+        <v>2521001663</v>
       </c>
       <c r="C88" t="s">
         <v>28</v>
@@ -3781,7 +4331,7 @@
         <v>29</v>
       </c>
       <c r="F88" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G88" s="1">
         <v>46044.475843321758</v>
@@ -3798,13 +4348,19 @@
       <c r="K88" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L88" t="s">
+        <v>105</v>
+      </c>
+      <c r="M88" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>73</v>
       </c>
-      <c r="B89" t="s">
-        <v>90</v>
+      <c r="B89">
+        <v>2521001663</v>
       </c>
       <c r="C89" t="s">
         <v>69</v>
@@ -3833,13 +4389,19 @@
       <c r="K89" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L89" t="s">
+        <v>105</v>
+      </c>
+      <c r="M89" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>73</v>
       </c>
-      <c r="B90" t="s">
-        <v>90</v>
+      <c r="B90">
+        <v>2521001663</v>
       </c>
       <c r="C90" t="s">
         <v>12</v>
@@ -3868,13 +4430,19 @@
       <c r="K90" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L90" t="s">
+        <v>105</v>
+      </c>
+      <c r="M90" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>73</v>
       </c>
-      <c r="B91" t="s">
-        <v>90</v>
+      <c r="B91">
+        <v>2521001663</v>
       </c>
       <c r="C91" t="s">
         <v>49</v>
@@ -3903,13 +4471,19 @@
       <c r="K91" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L91" t="s">
+        <v>105</v>
+      </c>
+      <c r="M91" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>73</v>
       </c>
-      <c r="B92" t="s">
-        <v>90</v>
+      <c r="B92">
+        <v>2521001663</v>
       </c>
       <c r="C92" t="s">
         <v>48</v>
@@ -3938,13 +4512,19 @@
       <c r="K92" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L92" t="s">
+        <v>105</v>
+      </c>
+      <c r="M92" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>73</v>
       </c>
-      <c r="B93" t="s">
-        <v>90</v>
+      <c r="B93">
+        <v>2521001663</v>
       </c>
       <c r="C93" t="s">
         <v>28</v>
@@ -3973,13 +4553,19 @@
       <c r="K93" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L93" t="s">
+        <v>105</v>
+      </c>
+      <c r="M93" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>73</v>
       </c>
-      <c r="B94" t="s">
-        <v>90</v>
+      <c r="B94">
+        <v>2521001663</v>
       </c>
       <c r="C94" t="s">
         <v>28</v>
@@ -4008,13 +4594,19 @@
       <c r="K94" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L94" t="s">
+        <v>105</v>
+      </c>
+      <c r="M94" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>73</v>
       </c>
-      <c r="B95" t="s">
-        <v>90</v>
+      <c r="B95">
+        <v>2521001663</v>
       </c>
       <c r="C95" t="s">
         <v>45</v>
@@ -4043,13 +4635,19 @@
       <c r="K95" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L95" t="s">
+        <v>105</v>
+      </c>
+      <c r="M95" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>73</v>
       </c>
-      <c r="B96" t="s">
-        <v>90</v>
+      <c r="B96">
+        <v>2521001663</v>
       </c>
       <c r="C96" t="s">
         <v>12</v>
@@ -4078,13 +4676,19 @@
       <c r="K96" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L96" t="s">
+        <v>105</v>
+      </c>
+      <c r="M96" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>73</v>
       </c>
-      <c r="B97" t="s">
-        <v>90</v>
+      <c r="B97">
+        <v>2521001663</v>
       </c>
       <c r="C97" t="s">
         <v>28</v>
@@ -4113,13 +4717,19 @@
       <c r="K97" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L97" t="s">
+        <v>105</v>
+      </c>
+      <c r="M97" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>73</v>
       </c>
-      <c r="B98" t="s">
-        <v>90</v>
+      <c r="B98">
+        <v>2521001663</v>
       </c>
       <c r="C98" t="s">
         <v>12</v>
@@ -4148,13 +4758,19 @@
       <c r="K98" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L98" t="s">
+        <v>105</v>
+      </c>
+      <c r="M98" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>73</v>
       </c>
-      <c r="B99" t="s">
-        <v>90</v>
+      <c r="B99">
+        <v>2521001663</v>
       </c>
       <c r="C99" t="s">
         <v>12</v>
@@ -4183,13 +4799,19 @@
       <c r="K99" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L99" t="s">
+        <v>105</v>
+      </c>
+      <c r="M99" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>73</v>
       </c>
-      <c r="B100" t="s">
-        <v>90</v>
+      <c r="B100">
+        <v>2521001663</v>
       </c>
       <c r="C100" t="s">
         <v>48</v>
@@ -4218,13 +4840,19 @@
       <c r="K100" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L100" t="s">
+        <v>105</v>
+      </c>
+      <c r="M100" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>73</v>
       </c>
-      <c r="B101" t="s">
-        <v>90</v>
+      <c r="B101">
+        <v>2521001663</v>
       </c>
       <c r="C101" t="s">
         <v>12</v>
@@ -4253,13 +4881,19 @@
       <c r="K101" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L101" t="s">
+        <v>105</v>
+      </c>
+      <c r="M101" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>73</v>
       </c>
-      <c r="B102" t="s">
-        <v>90</v>
+      <c r="B102">
+        <v>2521001663</v>
       </c>
       <c r="C102" t="s">
         <v>69</v>
@@ -4288,13 +4922,19 @@
       <c r="K102" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L102" t="s">
+        <v>105</v>
+      </c>
+      <c r="M102" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>73</v>
       </c>
-      <c r="B103" t="s">
-        <v>90</v>
+      <c r="B103">
+        <v>2521001663</v>
       </c>
       <c r="C103" t="s">
         <v>74</v>
@@ -4323,13 +4963,19 @@
       <c r="K103" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L103" t="s">
+        <v>105</v>
+      </c>
+      <c r="M103" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>73</v>
       </c>
-      <c r="B104" t="s">
-        <v>90</v>
+      <c r="B104">
+        <v>2521001663</v>
       </c>
       <c r="C104" t="s">
         <v>74</v>
@@ -4341,7 +4987,7 @@
         <v>29</v>
       </c>
       <c r="F104" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G104" s="1">
         <v>46057.490776539351</v>
@@ -4358,13 +5004,19 @@
       <c r="K104" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L104" t="s">
+        <v>105</v>
+      </c>
+      <c r="M104" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>73</v>
       </c>
-      <c r="B105" t="s">
-        <v>90</v>
+      <c r="B105">
+        <v>2521001663</v>
       </c>
       <c r="C105" t="s">
         <v>35</v>
@@ -4393,13 +5045,19 @@
       <c r="K105" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L105" t="s">
+        <v>105</v>
+      </c>
+      <c r="M105" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>73</v>
       </c>
-      <c r="B106" t="s">
-        <v>90</v>
+      <c r="B106">
+        <v>2521001663</v>
       </c>
       <c r="C106" t="s">
         <v>76</v>
@@ -4428,13 +5086,19 @@
       <c r="K106" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L106" t="s">
+        <v>105</v>
+      </c>
+      <c r="M106" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>73</v>
       </c>
-      <c r="B107" t="s">
-        <v>90</v>
+      <c r="B107">
+        <v>2521001663</v>
       </c>
       <c r="C107" t="s">
         <v>48</v>
@@ -4463,13 +5127,19 @@
       <c r="K107" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L107" t="s">
+        <v>105</v>
+      </c>
+      <c r="M107" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>73</v>
       </c>
-      <c r="B108" t="s">
-        <v>90</v>
+      <c r="B108">
+        <v>2521001663</v>
       </c>
       <c r="C108" t="s">
         <v>28</v>
@@ -4498,13 +5168,19 @@
       <c r="K108" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L108" t="s">
+        <v>105</v>
+      </c>
+      <c r="M108" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>73</v>
       </c>
-      <c r="B109" t="s">
-        <v>90</v>
+      <c r="B109">
+        <v>2521001663</v>
       </c>
       <c r="C109" t="s">
         <v>12</v>
@@ -4533,13 +5209,19 @@
       <c r="K109" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L109" t="s">
+        <v>105</v>
+      </c>
+      <c r="M109" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>73</v>
       </c>
-      <c r="B110" t="s">
-        <v>90</v>
+      <c r="B110">
+        <v>2521001663</v>
       </c>
       <c r="C110" t="s">
         <v>56</v>
@@ -4568,13 +5250,19 @@
       <c r="K110" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L110" t="s">
+        <v>105</v>
+      </c>
+      <c r="M110" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>73</v>
       </c>
-      <c r="B111" t="s">
-        <v>90</v>
+      <c r="B111">
+        <v>2521001663</v>
       </c>
       <c r="C111" t="s">
         <v>53</v>
@@ -4603,13 +5291,19 @@
       <c r="K111" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L111" t="s">
+        <v>105</v>
+      </c>
+      <c r="M111" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>73</v>
       </c>
-      <c r="B112" t="s">
-        <v>90</v>
+      <c r="B112">
+        <v>2521001663</v>
       </c>
       <c r="C112" t="s">
         <v>55</v>
@@ -4638,13 +5332,19 @@
       <c r="K112" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L112" t="s">
+        <v>105</v>
+      </c>
+      <c r="M112" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>73</v>
       </c>
-      <c r="B113" t="s">
-        <v>90</v>
+      <c r="B113">
+        <v>2521001663</v>
       </c>
       <c r="C113" t="s">
         <v>12</v>
@@ -4673,13 +5373,19 @@
       <c r="K113" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L113" t="s">
+        <v>105</v>
+      </c>
+      <c r="M113" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>73</v>
       </c>
-      <c r="B114" t="s">
-        <v>90</v>
+      <c r="B114">
+        <v>2521001663</v>
       </c>
       <c r="C114" t="s">
         <v>12</v>
@@ -4708,13 +5414,19 @@
       <c r="K114" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L114" t="s">
+        <v>105</v>
+      </c>
+      <c r="M114" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>73</v>
       </c>
-      <c r="B115" t="s">
-        <v>90</v>
+      <c r="B115">
+        <v>2521001663</v>
       </c>
       <c r="C115" t="s">
         <v>28</v>
@@ -4743,13 +5455,19 @@
       <c r="K115" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L115" t="s">
+        <v>105</v>
+      </c>
+      <c r="M115" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>73</v>
       </c>
-      <c r="B116" t="s">
-        <v>90</v>
+      <c r="B116">
+        <v>2521001663</v>
       </c>
       <c r="C116" t="s">
         <v>76</v>
@@ -4778,13 +5496,19 @@
       <c r="K116" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L116" t="s">
+        <v>105</v>
+      </c>
+      <c r="M116" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>73</v>
       </c>
-      <c r="B117" t="s">
-        <v>90</v>
+      <c r="B117">
+        <v>2521001663</v>
       </c>
       <c r="C117" t="s">
         <v>35</v>
@@ -4813,13 +5537,19 @@
       <c r="K117" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L117" t="s">
+        <v>105</v>
+      </c>
+      <c r="M117" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>73</v>
       </c>
-      <c r="B118" t="s">
-        <v>90</v>
+      <c r="B118">
+        <v>2521001663</v>
       </c>
       <c r="C118" t="s">
         <v>12</v>
@@ -4848,13 +5578,19 @@
       <c r="K118" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L118" t="s">
+        <v>105</v>
+      </c>
+      <c r="M118" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>73</v>
       </c>
-      <c r="B119" t="s">
-        <v>90</v>
+      <c r="B119">
+        <v>2521001663</v>
       </c>
       <c r="C119" t="s">
         <v>45</v>
@@ -4883,13 +5619,19 @@
       <c r="K119" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L119" t="s">
+        <v>105</v>
+      </c>
+      <c r="M119" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>73</v>
       </c>
-      <c r="B120" t="s">
-        <v>90</v>
+      <c r="B120">
+        <v>2521001663</v>
       </c>
       <c r="C120" t="s">
         <v>28</v>
@@ -4918,13 +5660,19 @@
       <c r="K120" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L120" t="s">
+        <v>105</v>
+      </c>
+      <c r="M120" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>73</v>
       </c>
-      <c r="B121" t="s">
-        <v>90</v>
+      <c r="B121">
+        <v>2521001663</v>
       </c>
       <c r="C121" t="s">
         <v>35</v>
@@ -4953,13 +5701,19 @@
       <c r="K121" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L121" t="s">
+        <v>105</v>
+      </c>
+      <c r="M121" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>73</v>
       </c>
-      <c r="B122" t="s">
-        <v>90</v>
+      <c r="B122">
+        <v>2521001663</v>
       </c>
       <c r="C122" t="s">
         <v>76</v>
@@ -4988,13 +5742,19 @@
       <c r="K122" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L122" t="s">
+        <v>105</v>
+      </c>
+      <c r="M122" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>73</v>
       </c>
-      <c r="B123" t="s">
-        <v>90</v>
+      <c r="B123">
+        <v>2521001663</v>
       </c>
       <c r="C123" t="s">
         <v>49</v>
@@ -5023,13 +5783,19 @@
       <c r="K123" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L123" t="s">
+        <v>105</v>
+      </c>
+      <c r="M123" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>73</v>
       </c>
-      <c r="B124" t="s">
-        <v>90</v>
+      <c r="B124">
+        <v>2521001663</v>
       </c>
       <c r="C124" t="s">
         <v>12</v>
@@ -5058,13 +5824,19 @@
       <c r="K124" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L124" t="s">
+        <v>105</v>
+      </c>
+      <c r="M124" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>73</v>
       </c>
-      <c r="B125" t="s">
-        <v>90</v>
+      <c r="B125">
+        <v>2521001663</v>
       </c>
       <c r="C125" t="s">
         <v>74</v>
@@ -5093,13 +5865,19 @@
       <c r="K125" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L125" t="s">
+        <v>105</v>
+      </c>
+      <c r="M125" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>73</v>
       </c>
-      <c r="B126" t="s">
-        <v>90</v>
+      <c r="B126">
+        <v>2521001663</v>
       </c>
       <c r="C126" t="s">
         <v>28</v>
@@ -5128,13 +5906,19 @@
       <c r="K126" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L126" t="s">
+        <v>105</v>
+      </c>
+      <c r="M126" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>73</v>
       </c>
-      <c r="B127" t="s">
-        <v>90</v>
+      <c r="B127">
+        <v>2521001663</v>
       </c>
       <c r="C127" t="s">
         <v>41</v>
@@ -5163,13 +5947,19 @@
       <c r="K127" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L127" t="s">
+        <v>105</v>
+      </c>
+      <c r="M127" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>73</v>
       </c>
-      <c r="B128" t="s">
-        <v>90</v>
+      <c r="B128">
+        <v>2521001663</v>
       </c>
       <c r="C128" t="s">
         <v>28</v>
@@ -5198,13 +5988,19 @@
       <c r="K128" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L128" t="s">
+        <v>105</v>
+      </c>
+      <c r="M128" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>73</v>
       </c>
-      <c r="B129" t="s">
-        <v>90</v>
+      <c r="B129">
+        <v>2521001663</v>
       </c>
       <c r="C129" t="s">
         <v>74</v>
@@ -5233,13 +6029,19 @@
       <c r="K129" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L129" t="s">
+        <v>105</v>
+      </c>
+      <c r="M129" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>73</v>
       </c>
-      <c r="B130" t="s">
-        <v>90</v>
+      <c r="B130">
+        <v>2521001663</v>
       </c>
       <c r="C130" t="s">
         <v>28</v>
@@ -5268,13 +6070,19 @@
       <c r="K130" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L130" t="s">
+        <v>105</v>
+      </c>
+      <c r="M130" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>73</v>
       </c>
-      <c r="B131" t="s">
-        <v>90</v>
+      <c r="B131">
+        <v>2521001663</v>
       </c>
       <c r="C131" t="s">
         <v>76</v>
@@ -5303,13 +6111,19 @@
       <c r="K131" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L131" t="s">
+        <v>105</v>
+      </c>
+      <c r="M131" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>73</v>
       </c>
-      <c r="B132" t="s">
-        <v>90</v>
+      <c r="B132">
+        <v>2521001663</v>
       </c>
       <c r="C132" t="s">
         <v>49</v>
@@ -5338,13 +6152,19 @@
       <c r="K132" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L132" t="s">
+        <v>105</v>
+      </c>
+      <c r="M132" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>73</v>
       </c>
-      <c r="B133" t="s">
-        <v>90</v>
+      <c r="B133">
+        <v>2521001663</v>
       </c>
       <c r="C133" t="s">
         <v>28</v>
@@ -5373,13 +6193,19 @@
       <c r="K133" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L133" t="s">
+        <v>105</v>
+      </c>
+      <c r="M133" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>73</v>
       </c>
-      <c r="B134" t="s">
-        <v>90</v>
+      <c r="B134">
+        <v>2521001663</v>
       </c>
       <c r="C134" t="s">
         <v>35</v>
@@ -5408,13 +6234,19 @@
       <c r="K134" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L134" t="s">
+        <v>105</v>
+      </c>
+      <c r="M134" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>73</v>
       </c>
-      <c r="B135" t="s">
-        <v>90</v>
+      <c r="B135">
+        <v>2521001663</v>
       </c>
       <c r="C135" t="s">
         <v>45</v>
@@ -5443,13 +6275,19 @@
       <c r="K135" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L135" t="s">
+        <v>105</v>
+      </c>
+      <c r="M135" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>73</v>
       </c>
-      <c r="B136" t="s">
-        <v>90</v>
+      <c r="B136">
+        <v>2521001663</v>
       </c>
       <c r="C136" t="s">
         <v>76</v>
@@ -5478,13 +6316,19 @@
       <c r="K136" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L136" t="s">
+        <v>105</v>
+      </c>
+      <c r="M136" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>73</v>
       </c>
-      <c r="B137" t="s">
-        <v>90</v>
+      <c r="B137">
+        <v>2521001663</v>
       </c>
       <c r="C137" t="s">
         <v>74</v>
@@ -5513,13 +6357,19 @@
       <c r="K137" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L137" t="s">
+        <v>105</v>
+      </c>
+      <c r="M137" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>73</v>
       </c>
-      <c r="B138" t="s">
-        <v>90</v>
+      <c r="B138">
+        <v>2521001663</v>
       </c>
       <c r="C138" t="s">
         <v>28</v>
@@ -5548,13 +6398,19 @@
       <c r="K138" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L138" t="s">
+        <v>105</v>
+      </c>
+      <c r="M138" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>73</v>
       </c>
-      <c r="B139" t="s">
-        <v>90</v>
+      <c r="B139">
+        <v>2521001663</v>
       </c>
       <c r="C139" t="s">
         <v>28</v>
@@ -5583,13 +6439,19 @@
       <c r="K139" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L139" t="s">
+        <v>105</v>
+      </c>
+      <c r="M139" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>73</v>
       </c>
-      <c r="B140" t="s">
-        <v>90</v>
+      <c r="B140">
+        <v>2521001663</v>
       </c>
       <c r="C140" t="s">
         <v>28</v>
@@ -5618,13 +6480,19 @@
       <c r="K140" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L140" t="s">
+        <v>105</v>
+      </c>
+      <c r="M140" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>73</v>
       </c>
-      <c r="B141" t="s">
-        <v>90</v>
+      <c r="B141">
+        <v>2521001663</v>
       </c>
       <c r="C141" t="s">
         <v>68</v>
@@ -5653,13 +6521,19 @@
       <c r="K141" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L141" t="s">
+        <v>105</v>
+      </c>
+      <c r="M141" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>73</v>
       </c>
-      <c r="B142" t="s">
-        <v>90</v>
+      <c r="B142">
+        <v>2521001663</v>
       </c>
       <c r="C142" t="s">
         <v>49</v>
@@ -5688,13 +6562,19 @@
       <c r="K142" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L142" t="s">
+        <v>105</v>
+      </c>
+      <c r="M142" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>73</v>
       </c>
-      <c r="B143" t="s">
-        <v>90</v>
+      <c r="B143">
+        <v>2521001663</v>
       </c>
       <c r="C143" t="s">
         <v>50</v>
@@ -5723,13 +6603,19 @@
       <c r="K143" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L143" t="s">
+        <v>105</v>
+      </c>
+      <c r="M143" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>73</v>
       </c>
-      <c r="B144" t="s">
-        <v>90</v>
+      <c r="B144">
+        <v>2521001663</v>
       </c>
       <c r="C144" t="s">
         <v>50</v>
@@ -5758,13 +6644,19 @@
       <c r="K144" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L144" t="s">
+        <v>105</v>
+      </c>
+      <c r="M144" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>73</v>
       </c>
-      <c r="B145" t="s">
-        <v>90</v>
+      <c r="B145">
+        <v>2521001663</v>
       </c>
       <c r="C145" t="s">
         <v>57</v>
@@ -5793,13 +6685,19 @@
       <c r="K145" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L145" t="s">
+        <v>105</v>
+      </c>
+      <c r="M145" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>73</v>
       </c>
-      <c r="B146" t="s">
-        <v>90</v>
+      <c r="B146">
+        <v>2521001663</v>
       </c>
       <c r="C146" t="s">
         <v>50</v>
@@ -5828,13 +6726,19 @@
       <c r="K146" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L146" t="s">
+        <v>105</v>
+      </c>
+      <c r="M146" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>73</v>
       </c>
-      <c r="B147" t="s">
-        <v>90</v>
+      <c r="B147">
+        <v>2521001663</v>
       </c>
       <c r="C147" t="s">
         <v>53</v>
@@ -5863,13 +6767,19 @@
       <c r="K147" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L147" t="s">
+        <v>105</v>
+      </c>
+      <c r="M147" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>73</v>
       </c>
-      <c r="B148" t="s">
-        <v>90</v>
+      <c r="B148">
+        <v>2521001663</v>
       </c>
       <c r="C148" t="s">
         <v>30</v>
@@ -5898,13 +6808,19 @@
       <c r="K148" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L148" t="s">
+        <v>105</v>
+      </c>
+      <c r="M148" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>73</v>
       </c>
-      <c r="B149" t="s">
-        <v>90</v>
+      <c r="B149">
+        <v>2521001663</v>
       </c>
       <c r="C149" t="s">
         <v>50</v>
@@ -5933,13 +6849,19 @@
       <c r="K149" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L149" t="s">
+        <v>105</v>
+      </c>
+      <c r="M149" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>73</v>
       </c>
-      <c r="B150" t="s">
-        <v>90</v>
+      <c r="B150">
+        <v>2521001663</v>
       </c>
       <c r="C150" t="s">
         <v>65</v>
@@ -5968,13 +6890,19 @@
       <c r="K150" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L150" t="s">
+        <v>105</v>
+      </c>
+      <c r="M150" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>73</v>
       </c>
-      <c r="B151" t="s">
-        <v>97</v>
+      <c r="B151">
+        <v>2521001668</v>
       </c>
       <c r="C151" t="s">
         <v>28</v>
@@ -6003,13 +6931,19 @@
       <c r="K151" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L151" t="s">
+        <v>106</v>
+      </c>
+      <c r="M151" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>73</v>
       </c>
-      <c r="B152" t="s">
-        <v>97</v>
+      <c r="B152">
+        <v>2521001668</v>
       </c>
       <c r="C152" t="s">
         <v>45</v>
@@ -6038,13 +6972,19 @@
       <c r="K152" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L152" t="s">
+        <v>106</v>
+      </c>
+      <c r="M152" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>73</v>
       </c>
-      <c r="B153" t="s">
-        <v>97</v>
+      <c r="B153">
+        <v>2521001668</v>
       </c>
       <c r="C153" t="s">
         <v>49</v>
@@ -6073,13 +7013,19 @@
       <c r="K153" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L153" t="s">
+        <v>106</v>
+      </c>
+      <c r="M153" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>73</v>
       </c>
-      <c r="B154" t="s">
-        <v>97</v>
+      <c r="B154">
+        <v>2521001668</v>
       </c>
       <c r="C154" t="s">
         <v>48</v>
@@ -6108,13 +7054,19 @@
       <c r="K154" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L154" t="s">
+        <v>106</v>
+      </c>
+      <c r="M154" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>73</v>
       </c>
-      <c r="B155" t="s">
-        <v>97</v>
+      <c r="B155">
+        <v>2521001668</v>
       </c>
       <c r="C155" t="s">
         <v>79</v>
@@ -6143,13 +7095,19 @@
       <c r="K155" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L155" t="s">
+        <v>106</v>
+      </c>
+      <c r="M155" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>73</v>
       </c>
-      <c r="B156" t="s">
-        <v>97</v>
+      <c r="B156">
+        <v>2521001668</v>
       </c>
       <c r="C156" t="s">
         <v>69</v>
@@ -6178,13 +7136,19 @@
       <c r="K156" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L156" t="s">
+        <v>106</v>
+      </c>
+      <c r="M156" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>73</v>
       </c>
-      <c r="B157" t="s">
-        <v>97</v>
+      <c r="B157">
+        <v>2521001668</v>
       </c>
       <c r="C157" t="s">
         <v>62</v>
@@ -6213,13 +7177,19 @@
       <c r="K157" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L157" t="s">
+        <v>106</v>
+      </c>
+      <c r="M157" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>73</v>
       </c>
-      <c r="B158" t="s">
-        <v>97</v>
+      <c r="B158">
+        <v>2521001668</v>
       </c>
       <c r="C158" t="s">
         <v>42</v>
@@ -6248,13 +7218,19 @@
       <c r="K158" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L158" t="s">
+        <v>106</v>
+      </c>
+      <c r="M158" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>73</v>
       </c>
-      <c r="B159" t="s">
-        <v>97</v>
+      <c r="B159">
+        <v>2521001668</v>
       </c>
       <c r="C159" t="s">
         <v>81</v>
@@ -6283,13 +7259,19 @@
       <c r="K159" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L159" t="s">
+        <v>106</v>
+      </c>
+      <c r="M159" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>73</v>
       </c>
-      <c r="B160" t="s">
-        <v>97</v>
+      <c r="B160">
+        <v>2521001668</v>
       </c>
       <c r="C160" t="s">
         <v>49</v>
@@ -6318,13 +7300,19 @@
       <c r="K160" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L160" t="s">
+        <v>106</v>
+      </c>
+      <c r="M160" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>73</v>
       </c>
-      <c r="B161" t="s">
-        <v>97</v>
+      <c r="B161">
+        <v>2521001668</v>
       </c>
       <c r="C161" t="s">
         <v>49</v>
@@ -6353,13 +7341,19 @@
       <c r="K161" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L161" t="s">
+        <v>106</v>
+      </c>
+      <c r="M161" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>73</v>
       </c>
-      <c r="B162" t="s">
-        <v>97</v>
+      <c r="B162">
+        <v>2521001668</v>
       </c>
       <c r="C162" t="s">
         <v>87</v>
@@ -6388,13 +7382,19 @@
       <c r="K162" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L162" t="s">
+        <v>106</v>
+      </c>
+      <c r="M162" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>73</v>
       </c>
-      <c r="B163" t="s">
-        <v>97</v>
+      <c r="B163">
+        <v>2521001668</v>
       </c>
       <c r="C163" t="s">
         <v>28</v>
@@ -6423,13 +7423,19 @@
       <c r="K163" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L163" t="s">
+        <v>106</v>
+      </c>
+      <c r="M163" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>73</v>
       </c>
-      <c r="B164" t="s">
-        <v>97</v>
+      <c r="B164">
+        <v>2521001668</v>
       </c>
       <c r="C164" t="s">
         <v>49</v>
@@ -6458,13 +7464,19 @@
       <c r="K164" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L164" t="s">
+        <v>106</v>
+      </c>
+      <c r="M164" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>73</v>
       </c>
-      <c r="B165" t="s">
-        <v>97</v>
+      <c r="B165">
+        <v>2521001668</v>
       </c>
       <c r="C165" t="s">
         <v>79</v>
@@ -6493,13 +7505,19 @@
       <c r="K165" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L165" t="s">
+        <v>106</v>
+      </c>
+      <c r="M165" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>73</v>
       </c>
-      <c r="B166" t="s">
-        <v>97</v>
+      <c r="B166">
+        <v>2521001668</v>
       </c>
       <c r="C166" t="s">
         <v>80</v>
@@ -6528,13 +7546,19 @@
       <c r="K166" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L166" t="s">
+        <v>106</v>
+      </c>
+      <c r="M166" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>73</v>
       </c>
-      <c r="B167" t="s">
-        <v>97</v>
+      <c r="B167">
+        <v>2521001668</v>
       </c>
       <c r="C167" t="s">
         <v>50</v>
@@ -6563,13 +7587,19 @@
       <c r="K167" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L167" t="s">
+        <v>106</v>
+      </c>
+      <c r="M167" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>73</v>
       </c>
-      <c r="B168" t="s">
-        <v>97</v>
+      <c r="B168">
+        <v>2521001668</v>
       </c>
       <c r="C168" t="s">
         <v>28</v>
@@ -6598,13 +7628,19 @@
       <c r="K168" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L168" t="s">
+        <v>106</v>
+      </c>
+      <c r="M168" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>73</v>
       </c>
-      <c r="B169" t="s">
-        <v>97</v>
+      <c r="B169">
+        <v>2521001668</v>
       </c>
       <c r="C169" t="s">
         <v>19</v>
@@ -6633,13 +7669,19 @@
       <c r="K169" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L169" t="s">
+        <v>106</v>
+      </c>
+      <c r="M169" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>73</v>
       </c>
-      <c r="B170" t="s">
-        <v>97</v>
+      <c r="B170">
+        <v>2521001668</v>
       </c>
       <c r="C170" t="s">
         <v>34</v>
@@ -6668,13 +7710,19 @@
       <c r="K170" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L170" t="s">
+        <v>106</v>
+      </c>
+      <c r="M170" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>73</v>
       </c>
-      <c r="B171" t="s">
-        <v>97</v>
+      <c r="B171">
+        <v>2521001668</v>
       </c>
       <c r="C171" t="s">
         <v>53</v>
@@ -6703,13 +7751,19 @@
       <c r="K171" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L171" t="s">
+        <v>106</v>
+      </c>
+      <c r="M171" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>73</v>
       </c>
-      <c r="B172" t="s">
-        <v>97</v>
+      <c r="B172">
+        <v>2521001668</v>
       </c>
       <c r="C172" t="s">
         <v>80</v>
@@ -6738,13 +7792,19 @@
       <c r="K172" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L172" t="s">
+        <v>106</v>
+      </c>
+      <c r="M172" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>73</v>
       </c>
-      <c r="B173" t="s">
-        <v>97</v>
+      <c r="B173">
+        <v>2521001668</v>
       </c>
       <c r="C173" t="s">
         <v>30</v>
@@ -6773,13 +7833,19 @@
       <c r="K173" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L173" t="s">
+        <v>106</v>
+      </c>
+      <c r="M173" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>73</v>
       </c>
-      <c r="B174" t="s">
-        <v>97</v>
+      <c r="B174">
+        <v>2521001668</v>
       </c>
       <c r="C174" t="s">
         <v>64</v>
@@ -6808,13 +7874,19 @@
       <c r="K174" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L174" t="s">
+        <v>106</v>
+      </c>
+      <c r="M174" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>73</v>
       </c>
-      <c r="B175" t="s">
-        <v>97</v>
+      <c r="B175">
+        <v>2521001668</v>
       </c>
       <c r="C175" t="s">
         <v>50</v>
@@ -6843,16 +7915,22 @@
       <c r="K175" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L175" t="s">
+        <v>106</v>
+      </c>
+      <c r="M175" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>73</v>
       </c>
-      <c r="B176" t="s">
-        <v>97</v>
+      <c r="B176">
+        <v>2521001668</v>
       </c>
       <c r="C176" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D176">
         <v>72</v>
@@ -6878,13 +7956,19 @@
       <c r="K176" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L176" t="s">
+        <v>106</v>
+      </c>
+      <c r="M176" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>73</v>
       </c>
-      <c r="B177" t="s">
-        <v>97</v>
+      <c r="B177">
+        <v>2521001668</v>
       </c>
       <c r="C177" t="s">
         <v>65</v>
@@ -6913,13 +7997,19 @@
       <c r="K177" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L177" t="s">
+        <v>106</v>
+      </c>
+      <c r="M177" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>73</v>
       </c>
-      <c r="B178" t="s">
-        <v>97</v>
+      <c r="B178">
+        <v>2521001668</v>
       </c>
       <c r="C178" t="s">
         <v>34</v>
@@ -6948,13 +8038,19 @@
       <c r="K178" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L178" t="s">
+        <v>106</v>
+      </c>
+      <c r="M178" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>73</v>
       </c>
-      <c r="B179" t="s">
-        <v>97</v>
+      <c r="B179">
+        <v>2521001668</v>
       </c>
       <c r="C179" t="s">
         <v>80</v>
@@ -6983,13 +8079,19 @@
       <c r="K179" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L179" t="s">
+        <v>106</v>
+      </c>
+      <c r="M179" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>73</v>
       </c>
-      <c r="B180" t="s">
-        <v>97</v>
+      <c r="B180">
+        <v>2521001668</v>
       </c>
       <c r="C180" t="s">
         <v>82</v>
@@ -7018,13 +8120,19 @@
       <c r="K180" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L180" t="s">
+        <v>106</v>
+      </c>
+      <c r="M180" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>73</v>
       </c>
-      <c r="B181" t="s">
-        <v>97</v>
+      <c r="B181">
+        <v>2521001668</v>
       </c>
       <c r="C181" t="s">
         <v>57</v>
@@ -7053,13 +8161,19 @@
       <c r="K181" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L181" t="s">
+        <v>106</v>
+      </c>
+      <c r="M181" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>73</v>
       </c>
-      <c r="B182" t="s">
-        <v>97</v>
+      <c r="B182">
+        <v>2521001668</v>
       </c>
       <c r="C182" t="s">
         <v>85</v>
@@ -7088,13 +8202,19 @@
       <c r="K182" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L182" t="s">
+        <v>106</v>
+      </c>
+      <c r="M182" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>73</v>
       </c>
-      <c r="B183" t="s">
-        <v>97</v>
+      <c r="B183">
+        <v>2521001668</v>
       </c>
       <c r="C183" t="s">
         <v>28</v>
@@ -7123,13 +8243,19 @@
       <c r="K183" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L183" t="s">
+        <v>106</v>
+      </c>
+      <c r="M183" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>73</v>
       </c>
-      <c r="B184" t="s">
-        <v>98</v>
+      <c r="B184">
+        <v>2521001662</v>
       </c>
       <c r="C184" t="s">
         <v>42</v>
@@ -7158,13 +8284,19 @@
       <c r="K184" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L184" t="s">
+        <v>107</v>
+      </c>
+      <c r="M184" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>73</v>
       </c>
-      <c r="B185" t="s">
-        <v>98</v>
+      <c r="B185">
+        <v>2521001662</v>
       </c>
       <c r="C185" t="s">
         <v>42</v>
@@ -7193,13 +8325,19 @@
       <c r="K185" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L185" t="s">
+        <v>107</v>
+      </c>
+      <c r="M185" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>73</v>
       </c>
-      <c r="B186" t="s">
-        <v>98</v>
+      <c r="B186">
+        <v>2521001662</v>
       </c>
       <c r="C186" t="s">
         <v>12</v>
@@ -7228,13 +8366,19 @@
       <c r="K186" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L186" t="s">
+        <v>107</v>
+      </c>
+      <c r="M186" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>73</v>
       </c>
-      <c r="B187" t="s">
-        <v>98</v>
+      <c r="B187">
+        <v>2521001662</v>
       </c>
       <c r="C187" t="s">
         <v>12</v>
@@ -7263,13 +8407,19 @@
       <c r="K187" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L187" t="s">
+        <v>107</v>
+      </c>
+      <c r="M187" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>73</v>
       </c>
-      <c r="B188" t="s">
-        <v>98</v>
+      <c r="B188">
+        <v>2521001662</v>
       </c>
       <c r="C188" t="s">
         <v>69</v>
@@ -7298,13 +8448,19 @@
       <c r="K188" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L188" t="s">
+        <v>107</v>
+      </c>
+      <c r="M188" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>73</v>
       </c>
-      <c r="B189" t="s">
-        <v>98</v>
+      <c r="B189">
+        <v>2521001662</v>
       </c>
       <c r="C189" t="s">
         <v>42</v>
@@ -7333,13 +8489,19 @@
       <c r="K189" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L189" t="s">
+        <v>107</v>
+      </c>
+      <c r="M189" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>73</v>
       </c>
-      <c r="B190" t="s">
-        <v>98</v>
+      <c r="B190">
+        <v>2521001662</v>
       </c>
       <c r="C190" t="s">
         <v>79</v>
@@ -7368,13 +8530,19 @@
       <c r="K190" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L190" t="s">
+        <v>107</v>
+      </c>
+      <c r="M190" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>73</v>
       </c>
-      <c r="B191" t="s">
-        <v>98</v>
+      <c r="B191">
+        <v>2521001662</v>
       </c>
       <c r="C191" t="s">
         <v>28</v>
@@ -7403,13 +8571,19 @@
       <c r="K191" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L191" t="s">
+        <v>107</v>
+      </c>
+      <c r="M191" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>73</v>
       </c>
-      <c r="B192" t="s">
-        <v>98</v>
+      <c r="B192">
+        <v>2521001662</v>
       </c>
       <c r="C192" t="s">
         <v>60</v>
@@ -7438,13 +8612,19 @@
       <c r="K192" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L192" t="s">
+        <v>107</v>
+      </c>
+      <c r="M192" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>73</v>
       </c>
-      <c r="B193" t="s">
-        <v>98</v>
+      <c r="B193">
+        <v>2521001662</v>
       </c>
       <c r="C193" t="s">
         <v>50</v>
@@ -7473,13 +8653,19 @@
       <c r="K193" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L193" t="s">
+        <v>107</v>
+      </c>
+      <c r="M193" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>73</v>
       </c>
-      <c r="B194" t="s">
-        <v>98</v>
+      <c r="B194">
+        <v>2521001662</v>
       </c>
       <c r="C194" t="s">
         <v>57</v>
@@ -7508,13 +8694,19 @@
       <c r="K194" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L194" t="s">
+        <v>107</v>
+      </c>
+      <c r="M194" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>73</v>
       </c>
-      <c r="B195" t="s">
-        <v>98</v>
+      <c r="B195">
+        <v>2521001662</v>
       </c>
       <c r="C195" t="s">
         <v>28</v>
@@ -7543,13 +8735,19 @@
       <c r="K195" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L195" t="s">
+        <v>107</v>
+      </c>
+      <c r="M195" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>73</v>
       </c>
-      <c r="B196" t="s">
-        <v>98</v>
+      <c r="B196">
+        <v>2521001662</v>
       </c>
       <c r="C196" t="s">
         <v>19</v>
@@ -7578,13 +8776,19 @@
       <c r="K196" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L196" t="s">
+        <v>107</v>
+      </c>
+      <c r="M196" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>73</v>
       </c>
-      <c r="B197" t="s">
-        <v>98</v>
+      <c r="B197">
+        <v>2521001662</v>
       </c>
       <c r="C197" t="s">
         <v>60</v>
@@ -7613,13 +8817,19 @@
       <c r="K197" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L197" t="s">
+        <v>107</v>
+      </c>
+      <c r="M197" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>73</v>
       </c>
-      <c r="B198" t="s">
-        <v>98</v>
+      <c r="B198">
+        <v>2521001662</v>
       </c>
       <c r="C198" t="s">
         <v>32</v>
@@ -7648,13 +8858,19 @@
       <c r="K198" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L198" t="s">
+        <v>107</v>
+      </c>
+      <c r="M198" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>73</v>
       </c>
-      <c r="B199" t="s">
-        <v>98</v>
+      <c r="B199">
+        <v>2521001662</v>
       </c>
       <c r="C199" t="s">
         <v>37</v>
@@ -7683,13 +8899,19 @@
       <c r="K199" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L199" t="s">
+        <v>107</v>
+      </c>
+      <c r="M199" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>73</v>
       </c>
-      <c r="B200" t="s">
-        <v>98</v>
+      <c r="B200">
+        <v>2521001662</v>
       </c>
       <c r="C200" t="s">
         <v>68</v>
@@ -7718,13 +8940,19 @@
       <c r="K200" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L200" t="s">
+        <v>107</v>
+      </c>
+      <c r="M200" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>73</v>
       </c>
-      <c r="B201" t="s">
-        <v>98</v>
+      <c r="B201">
+        <v>2521001662</v>
       </c>
       <c r="C201" t="s">
         <v>64</v>
@@ -7753,13 +8981,19 @@
       <c r="K201" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L201" t="s">
+        <v>107</v>
+      </c>
+      <c r="M201" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>73</v>
       </c>
-      <c r="B202" t="s">
-        <v>98</v>
+      <c r="B202">
+        <v>2521001662</v>
       </c>
       <c r="C202" t="s">
         <v>80</v>
@@ -7788,13 +9022,19 @@
       <c r="K202" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L202" t="s">
+        <v>107</v>
+      </c>
+      <c r="M202" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>73</v>
       </c>
-      <c r="B203" t="s">
-        <v>99</v>
+      <c r="B203">
+        <v>2521001661</v>
       </c>
       <c r="C203" t="s">
         <v>39</v>
@@ -7823,13 +9063,19 @@
       <c r="K203" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L203" t="s">
+        <v>106</v>
+      </c>
+      <c r="M203" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>73</v>
       </c>
-      <c r="B204" t="s">
-        <v>99</v>
+      <c r="B204">
+        <v>2521001661</v>
       </c>
       <c r="C204" t="s">
         <v>69</v>
@@ -7858,13 +9104,19 @@
       <c r="K204" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L204" t="s">
+        <v>106</v>
+      </c>
+      <c r="M204" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>73</v>
       </c>
-      <c r="B205" t="s">
-        <v>99</v>
+      <c r="B205">
+        <v>2521001661</v>
       </c>
       <c r="C205" t="s">
         <v>69</v>
@@ -7893,13 +9145,19 @@
       <c r="K205" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L205" t="s">
+        <v>106</v>
+      </c>
+      <c r="M205" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>73</v>
       </c>
-      <c r="B206" t="s">
-        <v>99</v>
+      <c r="B206">
+        <v>2521001661</v>
       </c>
       <c r="C206" t="s">
         <v>79</v>
@@ -7928,16 +9186,22 @@
       <c r="K206" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L206" t="s">
+        <v>106</v>
+      </c>
+      <c r="M206" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>73</v>
       </c>
-      <c r="B207" t="s">
-        <v>99</v>
+      <c r="B207">
+        <v>2521001661</v>
       </c>
       <c r="C207" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D207">
         <v>72</v>
@@ -7963,13 +9227,19 @@
       <c r="K207" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L207" t="s">
+        <v>106</v>
+      </c>
+      <c r="M207" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>73</v>
       </c>
-      <c r="B208" t="s">
-        <v>99</v>
+      <c r="B208">
+        <v>2521001661</v>
       </c>
       <c r="C208" t="s">
         <v>28</v>
@@ -7998,13 +9268,19 @@
       <c r="K208" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L208" t="s">
+        <v>106</v>
+      </c>
+      <c r="M208" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>73</v>
       </c>
-      <c r="B209" t="s">
-        <v>99</v>
+      <c r="B209">
+        <v>2521001661</v>
       </c>
       <c r="C209" t="s">
         <v>50</v>
@@ -8033,13 +9309,19 @@
       <c r="K209" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L209" t="s">
+        <v>106</v>
+      </c>
+      <c r="M209" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>73</v>
       </c>
-      <c r="B210" t="s">
-        <v>99</v>
+      <c r="B210">
+        <v>2521001661</v>
       </c>
       <c r="C210" t="s">
         <v>60</v>
@@ -8068,13 +9350,19 @@
       <c r="K210" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L210" t="s">
+        <v>106</v>
+      </c>
+      <c r="M210" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>73</v>
       </c>
-      <c r="B211" t="s">
-        <v>99</v>
+      <c r="B211">
+        <v>2521001661</v>
       </c>
       <c r="C211" t="s">
         <v>89</v>
@@ -8103,13 +9391,19 @@
       <c r="K211" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L211" t="s">
+        <v>106</v>
+      </c>
+      <c r="M211" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>73</v>
       </c>
-      <c r="B212" t="s">
-        <v>99</v>
+      <c r="B212">
+        <v>2521001661</v>
       </c>
       <c r="C212" t="s">
         <v>57</v>
@@ -8138,13 +9432,19 @@
       <c r="K212" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L212" t="s">
+        <v>106</v>
+      </c>
+      <c r="M212" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>73</v>
       </c>
-      <c r="B213" t="s">
-        <v>99</v>
+      <c r="B213">
+        <v>2521001661</v>
       </c>
       <c r="C213" t="s">
         <v>87</v>
@@ -8173,13 +9473,19 @@
       <c r="K213" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L213" t="s">
+        <v>106</v>
+      </c>
+      <c r="M213" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>73</v>
       </c>
-      <c r="B214" t="s">
-        <v>99</v>
+      <c r="B214">
+        <v>2521001661</v>
       </c>
       <c r="C214" t="s">
         <v>61</v>
@@ -8208,16 +9514,22 @@
       <c r="K214" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L214" t="s">
+        <v>106</v>
+      </c>
+      <c r="M214" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>73</v>
       </c>
-      <c r="B215" t="s">
-        <v>99</v>
+      <c r="B215">
+        <v>2521001661</v>
       </c>
       <c r="C215" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D215">
         <v>72</v>
@@ -8243,13 +9555,19 @@
       <c r="K215" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L215" t="s">
+        <v>106</v>
+      </c>
+      <c r="M215" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>73</v>
       </c>
-      <c r="B216" t="s">
-        <v>99</v>
+      <c r="B216">
+        <v>2521001661</v>
       </c>
       <c r="C216" t="s">
         <v>84</v>
@@ -8278,13 +9596,19 @@
       <c r="K216" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L216" t="s">
+        <v>106</v>
+      </c>
+      <c r="M216" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>73</v>
       </c>
-      <c r="B217" t="s">
-        <v>99</v>
+      <c r="B217">
+        <v>2521001661</v>
       </c>
       <c r="C217" t="s">
         <v>49</v>
@@ -8313,13 +9637,19 @@
       <c r="K217" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L217" t="s">
+        <v>106</v>
+      </c>
+      <c r="M217" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>73</v>
       </c>
-      <c r="B218" t="s">
-        <v>99</v>
+      <c r="B218">
+        <v>2521001661</v>
       </c>
       <c r="C218" t="s">
         <v>39</v>
@@ -8348,13 +9678,19 @@
       <c r="K218" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L218" t="s">
+        <v>106</v>
+      </c>
+      <c r="M218" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>106</v>
-      </c>
-      <c r="B219" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B219">
+        <v>2512000177</v>
       </c>
       <c r="C219" t="s">
         <v>48</v>
@@ -8383,13 +9719,19 @@
       <c r="K219" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L219" t="s">
+        <v>106</v>
+      </c>
+      <c r="M219" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>106</v>
-      </c>
-      <c r="B220" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B220">
+        <v>2512000177</v>
       </c>
       <c r="C220" t="s">
         <v>52</v>
@@ -8418,13 +9760,19 @@
       <c r="K220" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L220" t="s">
+        <v>106</v>
+      </c>
+      <c r="M220" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>106</v>
-      </c>
-      <c r="B221" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B221">
+        <v>2512000177</v>
       </c>
       <c r="C221" t="s">
         <v>48</v>
@@ -8453,13 +9801,19 @@
       <c r="K221" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L221" t="s">
+        <v>106</v>
+      </c>
+      <c r="M221" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>106</v>
-      </c>
-      <c r="B222" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B222">
+        <v>2512000177</v>
       </c>
       <c r="C222" t="s">
         <v>52</v>
@@ -8488,13 +9842,19 @@
       <c r="K222" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L222" t="s">
+        <v>106</v>
+      </c>
+      <c r="M222" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>106</v>
-      </c>
-      <c r="B223" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B223">
+        <v>2512000177</v>
       </c>
       <c r="C223" t="s">
         <v>76</v>
@@ -8523,13 +9883,19 @@
       <c r="K223" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L223" t="s">
+        <v>106</v>
+      </c>
+      <c r="M223" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>106</v>
-      </c>
-      <c r="B224" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B224">
+        <v>2512000177</v>
       </c>
       <c r="C224" t="s">
         <v>88</v>
@@ -8558,13 +9924,19 @@
       <c r="K224" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L224" t="s">
+        <v>106</v>
+      </c>
+      <c r="M224" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>106</v>
-      </c>
-      <c r="B225" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B225">
+        <v>2512000177</v>
       </c>
       <c r="C225" t="s">
         <v>84</v>
@@ -8593,13 +9965,19 @@
       <c r="K225" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L225" t="s">
+        <v>106</v>
+      </c>
+      <c r="M225" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>106</v>
-      </c>
-      <c r="B226" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B226">
+        <v>2512000177</v>
       </c>
       <c r="C226" t="s">
         <v>49</v>
@@ -8628,13 +10006,19 @@
       <c r="K226" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L226" t="s">
+        <v>106</v>
+      </c>
+      <c r="M226" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>106</v>
-      </c>
-      <c r="B227" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B227">
+        <v>2512000177</v>
       </c>
       <c r="C227" t="s">
         <v>39</v>
@@ -8663,13 +10047,19 @@
       <c r="K227" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L227" t="s">
+        <v>106</v>
+      </c>
+      <c r="M227" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>106</v>
-      </c>
-      <c r="B228" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B228">
+        <v>2512000177</v>
       </c>
       <c r="C228" t="s">
         <v>74</v>
@@ -8698,13 +10088,19 @@
       <c r="K228" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L228" t="s">
+        <v>106</v>
+      </c>
+      <c r="M228" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>106</v>
-      </c>
-      <c r="B229" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B229">
+        <v>2512000177</v>
       </c>
       <c r="C229" t="s">
         <v>59</v>
@@ -8733,13 +10129,19 @@
       <c r="K229" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L229" t="s">
+        <v>106</v>
+      </c>
+      <c r="M229" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>106</v>
-      </c>
-      <c r="B230" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B230">
+        <v>2512000177</v>
       </c>
       <c r="C230" t="s">
         <v>72</v>
@@ -8768,13 +10170,19 @@
       <c r="K230" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L230" t="s">
+        <v>106</v>
+      </c>
+      <c r="M230" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>106</v>
-      </c>
-      <c r="B231" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B231">
+        <v>2512000177</v>
       </c>
       <c r="C231" t="s">
         <v>71</v>
@@ -8803,13 +10211,19 @@
       <c r="K231" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L231" t="s">
+        <v>106</v>
+      </c>
+      <c r="M231" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>106</v>
-      </c>
-      <c r="B232" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B232">
+        <v>2512000177</v>
       </c>
       <c r="C232" t="s">
         <v>60</v>
@@ -8838,13 +10252,19 @@
       <c r="K232" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L232" t="s">
+        <v>106</v>
+      </c>
+      <c r="M232" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>106</v>
-      </c>
-      <c r="B233" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B233">
+        <v>2512000177</v>
       </c>
       <c r="C233" t="s">
         <v>43</v>
@@ -8873,13 +10293,19 @@
       <c r="K233" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L233" t="s">
+        <v>106</v>
+      </c>
+      <c r="M233" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>106</v>
-      </c>
-      <c r="B234" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B234">
+        <v>2512000177</v>
       </c>
       <c r="C234" t="s">
         <v>83</v>
@@ -8908,22 +10334,28 @@
       <c r="K234" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L234" t="s">
+        <v>106</v>
+      </c>
+      <c r="M234" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>106</v>
-      </c>
-      <c r="B235" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B235">
+        <v>2512000177</v>
       </c>
       <c r="C235" t="s">
+        <v>91</v>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+      <c r="E235" t="s">
         <v>92</v>
-      </c>
-      <c r="D235">
-        <v>0</v>
-      </c>
-      <c r="E235" t="s">
-        <v>93</v>
       </c>
       <c r="F235" t="s">
         <v>63</v>
@@ -8932,10 +10364,10 @@
         <v>45971.448405636576</v>
       </c>
       <c r="H235" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I235" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J235" t="s">
         <v>17</v>
@@ -8943,13 +10375,19 @@
       <c r="K235" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L235" t="s">
+        <v>106</v>
+      </c>
+      <c r="M235" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>106</v>
-      </c>
-      <c r="B236" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B236">
+        <v>2512000177</v>
       </c>
       <c r="C236" t="s">
         <v>48</v>
@@ -8978,13 +10416,19 @@
       <c r="K236" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L236" t="s">
+        <v>106</v>
+      </c>
+      <c r="M236" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>106</v>
-      </c>
-      <c r="B237" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B237">
+        <v>2512000177</v>
       </c>
       <c r="C237" t="s">
         <v>52</v>
@@ -9013,13 +10457,19 @@
       <c r="K237" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L237" t="s">
+        <v>106</v>
+      </c>
+      <c r="M237" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>106</v>
-      </c>
-      <c r="B238" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B238">
+        <v>2512000177</v>
       </c>
       <c r="C238" t="s">
         <v>76</v>
@@ -9048,13 +10498,19 @@
       <c r="K238" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L238" t="s">
+        <v>106</v>
+      </c>
+      <c r="M238" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>106</v>
-      </c>
-      <c r="B239" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B239">
+        <v>2512000177</v>
       </c>
       <c r="C239" t="s">
         <v>88</v>
@@ -9083,13 +10539,19 @@
       <c r="K239" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L239" t="s">
+        <v>106</v>
+      </c>
+      <c r="M239" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>106</v>
-      </c>
-      <c r="B240" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B240">
+        <v>2512000177</v>
       </c>
       <c r="C240" t="s">
         <v>84</v>
@@ -9118,13 +10580,19 @@
       <c r="K240" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L240" t="s">
+        <v>106</v>
+      </c>
+      <c r="M240" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>106</v>
-      </c>
-      <c r="B241" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B241">
+        <v>2512000177</v>
       </c>
       <c r="C241" t="s">
         <v>49</v>
@@ -9153,13 +10621,19 @@
       <c r="K241" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L241" t="s">
+        <v>106</v>
+      </c>
+      <c r="M241" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>106</v>
-      </c>
-      <c r="B242" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B242">
+        <v>2512000177</v>
       </c>
       <c r="C242" t="s">
         <v>39</v>
@@ -9188,13 +10662,19 @@
       <c r="K242" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L242" t="s">
+        <v>106</v>
+      </c>
+      <c r="M242" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>106</v>
-      </c>
-      <c r="B243" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B243">
+        <v>2512000177</v>
       </c>
       <c r="C243" t="s">
         <v>74</v>
@@ -9223,13 +10703,19 @@
       <c r="K243" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L243" t="s">
+        <v>106</v>
+      </c>
+      <c r="M243" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>106</v>
-      </c>
-      <c r="B244" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B244">
+        <v>2512000177</v>
       </c>
       <c r="C244" t="s">
         <v>59</v>
@@ -9258,13 +10744,19 @@
       <c r="K244" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L244" t="s">
+        <v>106</v>
+      </c>
+      <c r="M244" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>106</v>
-      </c>
-      <c r="B245" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B245">
+        <v>2512000177</v>
       </c>
       <c r="C245" t="s">
         <v>72</v>
@@ -9293,13 +10785,19 @@
       <c r="K245" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L245" t="s">
+        <v>106</v>
+      </c>
+      <c r="M245" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>106</v>
-      </c>
-      <c r="B246" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B246">
+        <v>2512000177</v>
       </c>
       <c r="C246" t="s">
         <v>71</v>
@@ -9328,13 +10826,19 @@
       <c r="K246" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L246" t="s">
+        <v>106</v>
+      </c>
+      <c r="M246" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>106</v>
-      </c>
-      <c r="B247" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B247">
+        <v>2512000177</v>
       </c>
       <c r="C247" t="s">
         <v>60</v>
@@ -9363,13 +10867,19 @@
       <c r="K247" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L247" t="s">
+        <v>106</v>
+      </c>
+      <c r="M247" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>106</v>
-      </c>
-      <c r="B248" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B248">
+        <v>2512000177</v>
       </c>
       <c r="C248" t="s">
         <v>84</v>
@@ -9398,13 +10908,19 @@
       <c r="K248" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L248" t="s">
+        <v>106</v>
+      </c>
+      <c r="M248" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>106</v>
-      </c>
-      <c r="B249" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B249">
+        <v>2512000177</v>
       </c>
       <c r="C249" t="s">
         <v>49</v>
@@ -9433,13 +10949,19 @@
       <c r="K249" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L249" t="s">
+        <v>106</v>
+      </c>
+      <c r="M249" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>106</v>
-      </c>
-      <c r="B250" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B250">
+        <v>2512000177</v>
       </c>
       <c r="C250" t="s">
         <v>39</v>
@@ -9468,13 +10990,19 @@
       <c r="K250" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L250" t="s">
+        <v>106</v>
+      </c>
+      <c r="M250" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>106</v>
-      </c>
-      <c r="B251" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B251">
+        <v>2512000177</v>
       </c>
       <c r="C251" t="s">
         <v>59</v>
@@ -9503,13 +11031,19 @@
       <c r="K251" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L251" t="s">
+        <v>106</v>
+      </c>
+      <c r="M251" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>106</v>
-      </c>
-      <c r="B252" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B252">
+        <v>2512000177</v>
       </c>
       <c r="C252" t="s">
         <v>28</v>
@@ -9538,13 +11072,19 @@
       <c r="K252" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L252" t="s">
+        <v>106</v>
+      </c>
+      <c r="M252" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>106</v>
-      </c>
-      <c r="B253" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B253">
+        <v>2512000177</v>
       </c>
       <c r="C253" t="s">
         <v>84</v>
@@ -9573,13 +11113,19 @@
       <c r="K253" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L253" t="s">
+        <v>106</v>
+      </c>
+      <c r="M253" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>106</v>
-      </c>
-      <c r="B254" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B254">
+        <v>2512000177</v>
       </c>
       <c r="C254" t="s">
         <v>59</v>
@@ -9608,13 +11154,19 @@
       <c r="K254" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L254" t="s">
+        <v>106</v>
+      </c>
+      <c r="M254" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>106</v>
-      </c>
-      <c r="B255" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B255">
+        <v>2512000177</v>
       </c>
       <c r="C255" t="s">
         <v>45</v>
@@ -9643,13 +11195,19 @@
       <c r="K255" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L255" t="s">
+        <v>106</v>
+      </c>
+      <c r="M255" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>106</v>
-      </c>
-      <c r="B256" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B256">
+        <v>2512000177</v>
       </c>
       <c r="C256" t="s">
         <v>76</v>
@@ -9678,13 +11236,19 @@
       <c r="K256" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L256" t="s">
+        <v>106</v>
+      </c>
+      <c r="M256" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>106</v>
-      </c>
-      <c r="B257" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B257">
+        <v>2512000177</v>
       </c>
       <c r="C257" t="s">
         <v>49</v>
@@ -9713,13 +11277,19 @@
       <c r="K257" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L257" t="s">
+        <v>106</v>
+      </c>
+      <c r="M257" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>106</v>
-      </c>
-      <c r="B258" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B258">
+        <v>2512000177</v>
       </c>
       <c r="C258" t="s">
         <v>84</v>
@@ -9748,13 +11318,19 @@
       <c r="K258" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L258" t="s">
+        <v>106</v>
+      </c>
+      <c r="M258" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>106</v>
-      </c>
-      <c r="B259" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B259">
+        <v>2512000177</v>
       </c>
       <c r="C259" t="s">
         <v>49</v>
@@ -9783,13 +11359,19 @@
       <c r="K259" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L259" t="s">
+        <v>106</v>
+      </c>
+      <c r="M259" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>106</v>
-      </c>
-      <c r="B260" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B260">
+        <v>2512000178</v>
       </c>
       <c r="C260" t="s">
         <v>48</v>
@@ -9818,13 +11400,22 @@
       <c r="K260" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L260" t="s">
+        <v>109</v>
+      </c>
+      <c r="M260" t="s">
+        <v>110</v>
+      </c>
+      <c r="N260" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>106</v>
-      </c>
-      <c r="B261" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B261">
+        <v>2512000178</v>
       </c>
       <c r="C261" t="s">
         <v>52</v>
@@ -9853,13 +11444,22 @@
       <c r="K261" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L261" t="s">
+        <v>109</v>
+      </c>
+      <c r="M261" t="s">
+        <v>110</v>
+      </c>
+      <c r="N261" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>106</v>
-      </c>
-      <c r="B262" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B262">
+        <v>2512000178</v>
       </c>
       <c r="C262" t="s">
         <v>48</v>
@@ -9888,13 +11488,22 @@
       <c r="K262" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L262" t="s">
+        <v>109</v>
+      </c>
+      <c r="M262" t="s">
+        <v>110</v>
+      </c>
+      <c r="N262" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>106</v>
-      </c>
-      <c r="B263" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B263">
+        <v>2512000178</v>
       </c>
       <c r="C263" t="s">
         <v>52</v>
@@ -9923,13 +11532,22 @@
       <c r="K263" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L263" t="s">
+        <v>109</v>
+      </c>
+      <c r="M263" t="s">
+        <v>110</v>
+      </c>
+      <c r="N263" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>106</v>
-      </c>
-      <c r="B264" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B264">
+        <v>2512000178</v>
       </c>
       <c r="C264" t="s">
         <v>48</v>
@@ -9958,13 +11576,22 @@
       <c r="K264" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L264" t="s">
+        <v>109</v>
+      </c>
+      <c r="M264" t="s">
+        <v>110</v>
+      </c>
+      <c r="N264" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>106</v>
-      </c>
-      <c r="B265" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B265">
+        <v>2512000178</v>
       </c>
       <c r="C265" t="s">
         <v>52</v>
@@ -9993,13 +11620,22 @@
       <c r="K265" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L265" t="s">
+        <v>109</v>
+      </c>
+      <c r="M265" t="s">
+        <v>110</v>
+      </c>
+      <c r="N265" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>106</v>
-      </c>
-      <c r="B266" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B266">
+        <v>2512000178</v>
       </c>
       <c r="C266" t="s">
         <v>48</v>
@@ -10028,13 +11664,22 @@
       <c r="K266" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L266" t="s">
+        <v>109</v>
+      </c>
+      <c r="M266" t="s">
+        <v>110</v>
+      </c>
+      <c r="N266" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>106</v>
-      </c>
-      <c r="B267" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B267">
+        <v>2512000178</v>
       </c>
       <c r="C267" t="s">
         <v>52</v>
@@ -10063,13 +11708,22 @@
       <c r="K267" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L267" t="s">
+        <v>109</v>
+      </c>
+      <c r="M267" t="s">
+        <v>110</v>
+      </c>
+      <c r="N267" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>106</v>
-      </c>
-      <c r="B268" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B268">
+        <v>2512000178</v>
       </c>
       <c r="C268" t="s">
         <v>48</v>
@@ -10098,13 +11752,22 @@
       <c r="K268" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L268" t="s">
+        <v>109</v>
+      </c>
+      <c r="M268" t="s">
+        <v>110</v>
+      </c>
+      <c r="N268" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>106</v>
-      </c>
-      <c r="B269" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B269">
+        <v>2512000178</v>
       </c>
       <c r="C269" t="s">
         <v>52</v>
@@ -10133,13 +11796,22 @@
       <c r="K269" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L269" t="s">
+        <v>109</v>
+      </c>
+      <c r="M269" t="s">
+        <v>110</v>
+      </c>
+      <c r="N269" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>106</v>
-      </c>
-      <c r="B270" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B270">
+        <v>2512000178</v>
       </c>
       <c r="C270" t="s">
         <v>48</v>
@@ -10168,13 +11840,22 @@
       <c r="K270" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L270" t="s">
+        <v>109</v>
+      </c>
+      <c r="M270" t="s">
+        <v>110</v>
+      </c>
+      <c r="N270" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>106</v>
-      </c>
-      <c r="B271" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B271">
+        <v>2512000178</v>
       </c>
       <c r="C271" t="s">
         <v>52</v>
@@ -10203,13 +11884,22 @@
       <c r="K271" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L271" t="s">
+        <v>109</v>
+      </c>
+      <c r="M271" t="s">
+        <v>110</v>
+      </c>
+      <c r="N271" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>106</v>
-      </c>
-      <c r="B272" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B272">
+        <v>2512000178</v>
       </c>
       <c r="C272" t="s">
         <v>47</v>
@@ -10238,13 +11928,19 @@
       <c r="K272" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L272" t="s">
+        <v>109</v>
+      </c>
+      <c r="M272" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>106</v>
-      </c>
-      <c r="B273" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B273">
+        <v>2512000178</v>
       </c>
       <c r="C273" t="s">
         <v>45</v>
@@ -10273,13 +11969,19 @@
       <c r="K273" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L273" t="s">
+        <v>109</v>
+      </c>
+      <c r="M273" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>106</v>
-      </c>
-      <c r="B274" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B274">
+        <v>2512000178</v>
       </c>
       <c r="C274" t="s">
         <v>76</v>
@@ -10308,13 +12010,19 @@
       <c r="K274" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L274" t="s">
+        <v>109</v>
+      </c>
+      <c r="M274" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>106</v>
-      </c>
-      <c r="B275" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B275">
+        <v>2512000178</v>
       </c>
       <c r="C275" t="s">
         <v>88</v>
@@ -10343,13 +12051,19 @@
       <c r="K275" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L275" t="s">
+        <v>109</v>
+      </c>
+      <c r="M275" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>106</v>
-      </c>
-      <c r="B276" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B276">
+        <v>2512000178</v>
       </c>
       <c r="C276" t="s">
         <v>49</v>
@@ -10378,13 +12092,19 @@
       <c r="K276" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L276" t="s">
+        <v>109</v>
+      </c>
+      <c r="M276" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>106</v>
-      </c>
-      <c r="B277" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B277">
+        <v>2512000178</v>
       </c>
       <c r="C277" t="s">
         <v>59</v>
@@ -10413,13 +12133,19 @@
       <c r="K277" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L277" t="s">
+        <v>109</v>
+      </c>
+      <c r="M277" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>106</v>
-      </c>
-      <c r="B278" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B278">
+        <v>2512000178</v>
       </c>
       <c r="C278" t="s">
         <v>28</v>
@@ -10448,13 +12174,19 @@
       <c r="K278" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L278" t="s">
+        <v>109</v>
+      </c>
+      <c r="M278" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>106</v>
-      </c>
-      <c r="B279" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B279">
+        <v>2512000178</v>
       </c>
       <c r="C279" t="s">
         <v>35</v>
@@ -10483,13 +12215,19 @@
       <c r="K279" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L279" t="s">
+        <v>109</v>
+      </c>
+      <c r="M279" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>106</v>
-      </c>
-      <c r="B280" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B280">
+        <v>2512000178</v>
       </c>
       <c r="C280" t="s">
         <v>45</v>
@@ -10518,16 +12256,22 @@
       <c r="K280" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L280" t="s">
+        <v>109</v>
+      </c>
+      <c r="M280" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>106</v>
-      </c>
-      <c r="B281" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B281">
+        <v>2512000178</v>
       </c>
       <c r="C281" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D281">
         <v>0</v>
@@ -10553,13 +12297,19 @@
       <c r="K281" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L281" t="s">
+        <v>109</v>
+      </c>
+      <c r="M281" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>106</v>
-      </c>
-      <c r="B282" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B282">
+        <v>2512000178</v>
       </c>
       <c r="C282" t="s">
         <v>75</v>
@@ -10588,13 +12338,19 @@
       <c r="K282" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L282" t="s">
+        <v>109</v>
+      </c>
+      <c r="M282" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>106</v>
-      </c>
-      <c r="B283" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B283">
+        <v>2512000178</v>
       </c>
       <c r="C283" t="s">
         <v>39</v>
@@ -10623,13 +12379,19 @@
       <c r="K283" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L283" t="s">
+        <v>109</v>
+      </c>
+      <c r="M283" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>106</v>
-      </c>
-      <c r="B284" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B284">
+        <v>2512000178</v>
       </c>
       <c r="C284" t="s">
         <v>48</v>
@@ -10658,13 +12420,22 @@
       <c r="K284" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L284" t="s">
+        <v>109</v>
+      </c>
+      <c r="M284" t="s">
+        <v>110</v>
+      </c>
+      <c r="N284" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>106</v>
-      </c>
-      <c r="B285" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B285">
+        <v>2512000178</v>
       </c>
       <c r="C285" t="s">
         <v>52</v>
@@ -10693,13 +12464,22 @@
       <c r="K285" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L285" t="s">
+        <v>109</v>
+      </c>
+      <c r="M285" t="s">
+        <v>110</v>
+      </c>
+      <c r="N285" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>106</v>
-      </c>
-      <c r="B286" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B286">
+        <v>2512000178</v>
       </c>
       <c r="C286" t="s">
         <v>48</v>
@@ -10728,13 +12508,22 @@
       <c r="K286" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L286" t="s">
+        <v>109</v>
+      </c>
+      <c r="M286" t="s">
+        <v>110</v>
+      </c>
+      <c r="N286" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>106</v>
-      </c>
-      <c r="B287" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B287">
+        <v>2512000178</v>
       </c>
       <c r="C287" t="s">
         <v>52</v>
@@ -10763,13 +12552,22 @@
       <c r="K287" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L287" t="s">
+        <v>109</v>
+      </c>
+      <c r="M287" t="s">
+        <v>110</v>
+      </c>
+      <c r="N287" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>106</v>
-      </c>
-      <c r="B288" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B288">
+        <v>2512000178</v>
       </c>
       <c r="C288" t="s">
         <v>48</v>
@@ -10798,13 +12596,22 @@
       <c r="K288" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L288" t="s">
+        <v>109</v>
+      </c>
+      <c r="M288" t="s">
+        <v>110</v>
+      </c>
+      <c r="N288" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>106</v>
-      </c>
-      <c r="B289" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B289">
+        <v>2512000178</v>
       </c>
       <c r="C289" t="s">
         <v>52</v>
@@ -10833,13 +12640,22 @@
       <c r="K289" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L289" t="s">
+        <v>109</v>
+      </c>
+      <c r="M289" t="s">
+        <v>110</v>
+      </c>
+      <c r="N289" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>106</v>
-      </c>
-      <c r="B290" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B290">
+        <v>2512000178</v>
       </c>
       <c r="C290" t="s">
         <v>45</v>
@@ -10868,13 +12684,19 @@
       <c r="K290" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L290" t="s">
+        <v>109</v>
+      </c>
+      <c r="M290" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>106</v>
-      </c>
-      <c r="B291" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B291">
+        <v>2512000178</v>
       </c>
       <c r="C291" t="s">
         <v>48</v>
@@ -10903,13 +12725,22 @@
       <c r="K291" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L291" t="s">
+        <v>109</v>
+      </c>
+      <c r="M291" t="s">
+        <v>110</v>
+      </c>
+      <c r="N291" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>106</v>
-      </c>
-      <c r="B292" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B292">
+        <v>2512000178</v>
       </c>
       <c r="C292" t="s">
         <v>52</v>
@@ -10938,13 +12769,22 @@
       <c r="K292" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L292" t="s">
+        <v>109</v>
+      </c>
+      <c r="M292" t="s">
+        <v>110</v>
+      </c>
+      <c r="N292" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>106</v>
-      </c>
-      <c r="B293" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B293">
+        <v>2512000178</v>
       </c>
       <c r="C293" t="s">
         <v>76</v>
@@ -10973,13 +12813,19 @@
       <c r="K293" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L293" t="s">
+        <v>109</v>
+      </c>
+      <c r="M293" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>106</v>
-      </c>
-      <c r="B294" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B294">
+        <v>2512000178</v>
       </c>
       <c r="C294" t="s">
         <v>39</v>
@@ -11008,13 +12854,19 @@
       <c r="K294" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L294" t="s">
+        <v>109</v>
+      </c>
+      <c r="M294" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>106</v>
-      </c>
-      <c r="B295" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B295">
+        <v>2512000178</v>
       </c>
       <c r="C295" t="s">
         <v>45</v>
@@ -11043,13 +12895,19 @@
       <c r="K295" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L295" t="s">
+        <v>109</v>
+      </c>
+      <c r="M295" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>106</v>
-      </c>
-      <c r="B296" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B296">
+        <v>2512000178</v>
       </c>
       <c r="C296" t="s">
         <v>12</v>
@@ -11078,13 +12936,22 @@
       <c r="K296" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L296" t="s">
+        <v>109</v>
+      </c>
+      <c r="M296" t="s">
+        <v>110</v>
+      </c>
+      <c r="N296" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>106</v>
-      </c>
-      <c r="B297" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B297">
+        <v>2512000178</v>
       </c>
       <c r="C297" t="s">
         <v>12</v>
@@ -11113,13 +12980,22 @@
       <c r="K297" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L297" t="s">
+        <v>109</v>
+      </c>
+      <c r="M297" t="s">
+        <v>110</v>
+      </c>
+      <c r="N297" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>106</v>
-      </c>
-      <c r="B298" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B298">
+        <v>2512000178</v>
       </c>
       <c r="C298" t="s">
         <v>39</v>
@@ -11148,13 +13024,19 @@
       <c r="K298" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L298" t="s">
+        <v>109</v>
+      </c>
+      <c r="M298" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>106</v>
-      </c>
-      <c r="B299" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B299">
+        <v>2512000178</v>
       </c>
       <c r="C299" t="s">
         <v>48</v>
@@ -11183,13 +13065,22 @@
       <c r="K299" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L299" t="s">
+        <v>109</v>
+      </c>
+      <c r="M299" t="s">
+        <v>110</v>
+      </c>
+      <c r="N299" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>106</v>
-      </c>
-      <c r="B300" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B300">
+        <v>2512000178</v>
       </c>
       <c r="C300" t="s">
         <v>52</v>
@@ -11218,13 +13109,22 @@
       <c r="K300" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L300" t="s">
+        <v>109</v>
+      </c>
+      <c r="M300" t="s">
+        <v>110</v>
+      </c>
+      <c r="N300" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>106</v>
-      </c>
-      <c r="B301" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B301">
+        <v>2512000178</v>
       </c>
       <c r="C301" t="s">
         <v>48</v>
@@ -11253,13 +13153,22 @@
       <c r="K301" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L301" t="s">
+        <v>109</v>
+      </c>
+      <c r="M301" t="s">
+        <v>110</v>
+      </c>
+      <c r="N301" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>106</v>
-      </c>
-      <c r="B302" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B302">
+        <v>2512000178</v>
       </c>
       <c r="C302" t="s">
         <v>52</v>
@@ -11288,13 +13197,22 @@
       <c r="K302" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L302" t="s">
+        <v>109</v>
+      </c>
+      <c r="M302" t="s">
+        <v>110</v>
+      </c>
+      <c r="N302" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>106</v>
-      </c>
-      <c r="B303" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B303">
+        <v>2512000178</v>
       </c>
       <c r="C303" t="s">
         <v>48</v>
@@ -11323,13 +13241,22 @@
       <c r="K303" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L303" t="s">
+        <v>109</v>
+      </c>
+      <c r="M303" t="s">
+        <v>110</v>
+      </c>
+      <c r="N303" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>106</v>
-      </c>
-      <c r="B304" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B304">
+        <v>2512000178</v>
       </c>
       <c r="C304" t="s">
         <v>52</v>
@@ -11358,13 +13285,22 @@
       <c r="K304" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L304" t="s">
+        <v>109</v>
+      </c>
+      <c r="M304" t="s">
+        <v>110</v>
+      </c>
+      <c r="N304" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>106</v>
-      </c>
-      <c r="B305" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B305">
+        <v>2512000178</v>
       </c>
       <c r="C305" t="s">
         <v>48</v>
@@ -11393,13 +13329,22 @@
       <c r="K305" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L305" t="s">
+        <v>109</v>
+      </c>
+      <c r="M305" t="s">
+        <v>110</v>
+      </c>
+      <c r="N305" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>106</v>
-      </c>
-      <c r="B306" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B306">
+        <v>2512000178</v>
       </c>
       <c r="C306" t="s">
         <v>52</v>
@@ -11428,13 +13373,22 @@
       <c r="K306" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L306" t="s">
+        <v>109</v>
+      </c>
+      <c r="M306" t="s">
+        <v>110</v>
+      </c>
+      <c r="N306" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>106</v>
-      </c>
-      <c r="B307" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B307">
+        <v>2512000178</v>
       </c>
       <c r="C307" t="s">
         <v>48</v>
@@ -11463,13 +13417,22 @@
       <c r="K307" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L307" t="s">
+        <v>109</v>
+      </c>
+      <c r="M307" t="s">
+        <v>110</v>
+      </c>
+      <c r="N307" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>106</v>
-      </c>
-      <c r="B308" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B308">
+        <v>2512000178</v>
       </c>
       <c r="C308" t="s">
         <v>52</v>
@@ -11498,13 +13461,22 @@
       <c r="K308" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L308" t="s">
+        <v>109</v>
+      </c>
+      <c r="M308" t="s">
+        <v>110</v>
+      </c>
+      <c r="N308" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>106</v>
-      </c>
-      <c r="B309" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B309">
+        <v>2512000178</v>
       </c>
       <c r="C309" t="s">
         <v>76</v>
@@ -11533,13 +13505,19 @@
       <c r="K309" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L309" t="s">
+        <v>109</v>
+      </c>
+      <c r="M309" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>106</v>
-      </c>
-      <c r="B310" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B310">
+        <v>2512000178</v>
       </c>
       <c r="C310" t="s">
         <v>49</v>
@@ -11568,13 +13546,19 @@
       <c r="K310" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L310" t="s">
+        <v>109</v>
+      </c>
+      <c r="M310" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>106</v>
-      </c>
-      <c r="B311" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B311">
+        <v>2512000178</v>
       </c>
       <c r="C311" t="s">
         <v>39</v>
@@ -11603,13 +13587,19 @@
       <c r="K311" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L311" t="s">
+        <v>109</v>
+      </c>
+      <c r="M311" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>106</v>
-      </c>
-      <c r="B312" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B312">
+        <v>2512000178</v>
       </c>
       <c r="C312" t="s">
         <v>59</v>
@@ -11638,13 +13628,19 @@
       <c r="K312" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L312" t="s">
+        <v>109</v>
+      </c>
+      <c r="M312" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>106</v>
-      </c>
-      <c r="B313" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B313">
+        <v>2512000178</v>
       </c>
       <c r="C313" t="s">
         <v>45</v>
@@ -11673,13 +13669,19 @@
       <c r="K313" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L313" t="s">
+        <v>109</v>
+      </c>
+      <c r="M313" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>106</v>
-      </c>
-      <c r="B314" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B314">
+        <v>2512000178</v>
       </c>
       <c r="C314" t="s">
         <v>76</v>
@@ -11708,13 +13710,19 @@
       <c r="K314" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L314" t="s">
+        <v>109</v>
+      </c>
+      <c r="M314" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>106</v>
-      </c>
-      <c r="B315" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B315">
+        <v>2512000178</v>
       </c>
       <c r="C315" t="s">
         <v>38</v>
@@ -11743,13 +13751,19 @@
       <c r="K315" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L315" t="s">
+        <v>109</v>
+      </c>
+      <c r="M315" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>106</v>
-      </c>
-      <c r="B316" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B316">
+        <v>2512000178</v>
       </c>
       <c r="C316" t="s">
         <v>28</v>
@@ -11778,13 +13792,19 @@
       <c r="K316" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L316" t="s">
+        <v>109</v>
+      </c>
+      <c r="M316" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>106</v>
-      </c>
-      <c r="B317" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B317">
+        <v>2512000178</v>
       </c>
       <c r="C317" t="s">
         <v>49</v>
@@ -11813,13 +13833,19 @@
       <c r="K317" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L317" t="s">
+        <v>109</v>
+      </c>
+      <c r="M317" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>106</v>
-      </c>
-      <c r="B318" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B318">
+        <v>2512000178</v>
       </c>
       <c r="C318" t="s">
         <v>76</v>
@@ -11848,13 +13874,19 @@
       <c r="K318" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L318" t="s">
+        <v>109</v>
+      </c>
+      <c r="M318" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>106</v>
-      </c>
-      <c r="B319" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B319">
+        <v>2512000178</v>
       </c>
       <c r="C319" t="s">
         <v>12</v>
@@ -11883,13 +13915,22 @@
       <c r="K319" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L319" t="s">
+        <v>109</v>
+      </c>
+      <c r="M319" t="s">
+        <v>110</v>
+      </c>
+      <c r="N319" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>106</v>
-      </c>
-      <c r="B320" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B320">
+        <v>2512000178</v>
       </c>
       <c r="C320" t="s">
         <v>12</v>
@@ -11918,13 +13959,22 @@
       <c r="K320" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L320" t="s">
+        <v>109</v>
+      </c>
+      <c r="M320" t="s">
+        <v>110</v>
+      </c>
+      <c r="N320" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>106</v>
-      </c>
-      <c r="B321" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B321">
+        <v>2512000178</v>
       </c>
       <c r="C321" t="s">
         <v>12</v>
@@ -11953,13 +14003,22 @@
       <c r="K321" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L321" t="s">
+        <v>109</v>
+      </c>
+      <c r="M321" t="s">
+        <v>110</v>
+      </c>
+      <c r="N321" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>106</v>
-      </c>
-      <c r="B322" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B322">
+        <v>2512000178</v>
       </c>
       <c r="C322" t="s">
         <v>69</v>
@@ -11988,13 +14047,19 @@
       <c r="K322" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L322" t="s">
+        <v>109</v>
+      </c>
+      <c r="M322" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>106</v>
-      </c>
-      <c r="B323" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B323">
+        <v>2512000178</v>
       </c>
       <c r="C323" t="s">
         <v>48</v>
@@ -12023,13 +14088,22 @@
       <c r="K323" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L323" t="s">
+        <v>109</v>
+      </c>
+      <c r="M323" t="s">
+        <v>110</v>
+      </c>
+      <c r="N323" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>106</v>
-      </c>
-      <c r="B324" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B324">
+        <v>2512000178</v>
       </c>
       <c r="C324" t="s">
         <v>48</v>
@@ -12058,13 +14132,22 @@
       <c r="K324" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L324" t="s">
+        <v>109</v>
+      </c>
+      <c r="M324" t="s">
+        <v>110</v>
+      </c>
+      <c r="N324" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>106</v>
-      </c>
-      <c r="B325" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B325">
+        <v>2512000178</v>
       </c>
       <c r="C325" t="s">
         <v>52</v>
@@ -12093,13 +14176,22 @@
       <c r="K325" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L325" t="s">
+        <v>109</v>
+      </c>
+      <c r="M325" t="s">
+        <v>110</v>
+      </c>
+      <c r="N325" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>106</v>
-      </c>
-      <c r="B326" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B326">
+        <v>2512000178</v>
       </c>
       <c r="C326" t="s">
         <v>52</v>
@@ -12128,13 +14220,22 @@
       <c r="K326" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L326" t="s">
+        <v>109</v>
+      </c>
+      <c r="M326" t="s">
+        <v>110</v>
+      </c>
+      <c r="N326" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>106</v>
-      </c>
-      <c r="B327" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B327">
+        <v>2512000178</v>
       </c>
       <c r="C327" t="s">
         <v>48</v>
@@ -12163,13 +14264,22 @@
       <c r="K327" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L327" t="s">
+        <v>109</v>
+      </c>
+      <c r="M327" t="s">
+        <v>110</v>
+      </c>
+      <c r="N327" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>106</v>
-      </c>
-      <c r="B328" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B328">
+        <v>2512000178</v>
       </c>
       <c r="C328" t="s">
         <v>52</v>
@@ -12198,13 +14308,22 @@
       <c r="K328" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L328" t="s">
+        <v>109</v>
+      </c>
+      <c r="M328" t="s">
+        <v>110</v>
+      </c>
+      <c r="N328" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>106</v>
-      </c>
-      <c r="B329" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B329">
+        <v>2512000178</v>
       </c>
       <c r="C329" t="s">
         <v>48</v>
@@ -12233,13 +14352,22 @@
       <c r="K329" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L329" t="s">
+        <v>109</v>
+      </c>
+      <c r="M329" t="s">
+        <v>110</v>
+      </c>
+      <c r="N329" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>106</v>
-      </c>
-      <c r="B330" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B330">
+        <v>2512000178</v>
       </c>
       <c r="C330" t="s">
         <v>48</v>
@@ -12268,13 +14396,22 @@
       <c r="K330" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L330" t="s">
+        <v>109</v>
+      </c>
+      <c r="M330" t="s">
+        <v>110</v>
+      </c>
+      <c r="N330" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>106</v>
-      </c>
-      <c r="B331" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B331">
+        <v>2512000178</v>
       </c>
       <c r="C331" t="s">
         <v>52</v>
@@ -12303,13 +14440,22 @@
       <c r="K331" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L331" t="s">
+        <v>109</v>
+      </c>
+      <c r="M331" t="s">
+        <v>110</v>
+      </c>
+      <c r="N331" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>106</v>
-      </c>
-      <c r="B332" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B332">
+        <v>2512000178</v>
       </c>
       <c r="C332" t="s">
         <v>52</v>
@@ -12338,13 +14484,22 @@
       <c r="K332" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L332" t="s">
+        <v>109</v>
+      </c>
+      <c r="M332" t="s">
+        <v>110</v>
+      </c>
+      <c r="N332" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>106</v>
-      </c>
-      <c r="B333" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B333">
+        <v>2512000178</v>
       </c>
       <c r="C333" t="s">
         <v>48</v>
@@ -12373,13 +14528,22 @@
       <c r="K333" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L333" t="s">
+        <v>109</v>
+      </c>
+      <c r="M333" t="s">
+        <v>110</v>
+      </c>
+      <c r="N333" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>106</v>
-      </c>
-      <c r="B334" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B334">
+        <v>2512000178</v>
       </c>
       <c r="C334" t="s">
         <v>52</v>
@@ -12408,13 +14572,22 @@
       <c r="K334" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L334" t="s">
+        <v>109</v>
+      </c>
+      <c r="M334" t="s">
+        <v>110</v>
+      </c>
+      <c r="N334" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>106</v>
-      </c>
-      <c r="B335" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B335">
+        <v>2512000178</v>
       </c>
       <c r="C335" t="s">
         <v>28</v>
@@ -12443,13 +14616,19 @@
       <c r="K335" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L335" t="s">
+        <v>109</v>
+      </c>
+      <c r="M335" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>106</v>
-      </c>
-      <c r="B336" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B336">
+        <v>2512000178</v>
       </c>
       <c r="C336" t="s">
         <v>60</v>
@@ -12478,13 +14657,19 @@
       <c r="K336" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L336" t="s">
+        <v>109</v>
+      </c>
+      <c r="M336" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>106</v>
-      </c>
-      <c r="B337" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B337">
+        <v>2512000178</v>
       </c>
       <c r="C337" t="s">
         <v>60</v>
@@ -12513,13 +14698,19 @@
       <c r="K337" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L337" t="s">
+        <v>109</v>
+      </c>
+      <c r="M337" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>106</v>
-      </c>
-      <c r="B338" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B338">
+        <v>2512000178</v>
       </c>
       <c r="C338" t="s">
         <v>60</v>
@@ -12548,13 +14739,19 @@
       <c r="K338" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L338" t="s">
+        <v>109</v>
+      </c>
+      <c r="M338" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>106</v>
-      </c>
-      <c r="B339" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B339">
+        <v>2512000178</v>
       </c>
       <c r="C339" t="s">
         <v>28</v>
@@ -12583,13 +14780,19 @@
       <c r="K339" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L339" t="s">
+        <v>109</v>
+      </c>
+      <c r="M339" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>106</v>
-      </c>
-      <c r="B340" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B340">
+        <v>2512000178</v>
       </c>
       <c r="C340" t="s">
         <v>50</v>
@@ -12618,13 +14821,19 @@
       <c r="K340" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L340" t="s">
+        <v>109</v>
+      </c>
+      <c r="M340" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>106</v>
-      </c>
-      <c r="B341" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B341">
+        <v>2512000178</v>
       </c>
       <c r="C341" t="s">
         <v>50</v>
@@ -12653,13 +14862,19 @@
       <c r="K341" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L341" t="s">
+        <v>109</v>
+      </c>
+      <c r="M341" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>106</v>
-      </c>
-      <c r="B342" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B342">
+        <v>2512000178</v>
       </c>
       <c r="C342" t="s">
         <v>60</v>
@@ -12688,13 +14903,19 @@
       <c r="K342" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L342" t="s">
+        <v>109</v>
+      </c>
+      <c r="M342" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>106</v>
-      </c>
-      <c r="B343" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B343">
+        <v>2512000178</v>
       </c>
       <c r="C343" t="s">
         <v>50</v>
@@ -12723,13 +14944,19 @@
       <c r="K343" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L343" t="s">
+        <v>109</v>
+      </c>
+      <c r="M343" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>106</v>
-      </c>
-      <c r="B344" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B344">
+        <v>2512000178</v>
       </c>
       <c r="C344" t="s">
         <v>28</v>
@@ -12758,13 +14985,19 @@
       <c r="K344" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L344" t="s">
+        <v>109</v>
+      </c>
+      <c r="M344" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>106</v>
-      </c>
-      <c r="B345" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B345">
+        <v>2512000178</v>
       </c>
       <c r="C345" t="s">
         <v>60</v>
@@ -12793,13 +15026,19 @@
       <c r="K345" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L345" t="s">
+        <v>109</v>
+      </c>
+      <c r="M345" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>106</v>
-      </c>
-      <c r="B346" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B346">
+        <v>2512000178</v>
       </c>
       <c r="C346" t="s">
         <v>60</v>
@@ -12828,13 +15067,19 @@
       <c r="K346" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L346" t="s">
+        <v>109</v>
+      </c>
+      <c r="M346" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>106</v>
-      </c>
-      <c r="B347" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B347">
+        <v>2512000178</v>
       </c>
       <c r="C347" t="s">
         <v>60</v>
@@ -12863,13 +15108,19 @@
       <c r="K347" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L347" t="s">
+        <v>109</v>
+      </c>
+      <c r="M347" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>106</v>
-      </c>
-      <c r="B348" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B348">
+        <v>2512000178</v>
       </c>
       <c r="C348" t="s">
         <v>50</v>
@@ -12898,13 +15149,19 @@
       <c r="K348" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L348" t="s">
+        <v>109</v>
+      </c>
+      <c r="M348" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>106</v>
-      </c>
-      <c r="B349" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B349">
+        <v>2512000178</v>
       </c>
       <c r="C349" t="s">
         <v>50</v>
@@ -12933,13 +15190,19 @@
       <c r="K349" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L349" t="s">
+        <v>109</v>
+      </c>
+      <c r="M349" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>106</v>
-      </c>
-      <c r="B350" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="B350">
+        <v>2512000178</v>
       </c>
       <c r="C350" t="s">
         <v>50</v>
@@ -12968,13 +15231,19 @@
       <c r="K350" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L350" t="s">
+        <v>109</v>
+      </c>
+      <c r="M350" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>106</v>
-      </c>
-      <c r="B351" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B351">
+        <v>2512000176</v>
       </c>
       <c r="C351" t="s">
         <v>48</v>
@@ -13003,13 +15272,19 @@
       <c r="K351" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L351" t="s">
+        <v>106</v>
+      </c>
+      <c r="M351" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>106</v>
-      </c>
-      <c r="B352" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B352">
+        <v>2512000176</v>
       </c>
       <c r="C352" t="s">
         <v>52</v>
@@ -13038,13 +15313,19 @@
       <c r="K352" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L352" t="s">
+        <v>106</v>
+      </c>
+      <c r="M352" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>106</v>
-      </c>
-      <c r="B353" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B353">
+        <v>2512000176</v>
       </c>
       <c r="C353" t="s">
         <v>76</v>
@@ -13073,13 +15354,19 @@
       <c r="K353" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L353" t="s">
+        <v>106</v>
+      </c>
+      <c r="M353" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>106</v>
-      </c>
-      <c r="B354" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B354">
+        <v>2512000176</v>
       </c>
       <c r="C354" t="s">
         <v>49</v>
@@ -13108,13 +15395,19 @@
       <c r="K354" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L354" t="s">
+        <v>106</v>
+      </c>
+      <c r="M354" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>106</v>
-      </c>
-      <c r="B355" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B355">
+        <v>2512000176</v>
       </c>
       <c r="C355" t="s">
         <v>59</v>
@@ -13143,13 +15436,19 @@
       <c r="K355" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L355" t="s">
+        <v>106</v>
+      </c>
+      <c r="M355" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>106</v>
-      </c>
-      <c r="B356" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B356">
+        <v>2512000176</v>
       </c>
       <c r="C356" t="s">
         <v>60</v>
@@ -13178,13 +15477,19 @@
       <c r="K356" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L356" t="s">
+        <v>106</v>
+      </c>
+      <c r="M356" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>106</v>
-      </c>
-      <c r="B357" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B357">
+        <v>2512000176</v>
       </c>
       <c r="C357" t="s">
         <v>84</v>
@@ -13213,13 +15518,19 @@
       <c r="K357" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L357" t="s">
+        <v>106</v>
+      </c>
+      <c r="M357" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>106</v>
-      </c>
-      <c r="B358" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B358">
+        <v>2512000176</v>
       </c>
       <c r="C358" t="s">
         <v>49</v>
@@ -13248,13 +15559,19 @@
       <c r="K358" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L358" t="s">
+        <v>106</v>
+      </c>
+      <c r="M358" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>106</v>
-      </c>
-      <c r="B359" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B359">
+        <v>2512000176</v>
       </c>
       <c r="C359" t="s">
         <v>69</v>
@@ -13283,13 +15600,19 @@
       <c r="K359" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L359" t="s">
+        <v>106</v>
+      </c>
+      <c r="M359" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>106</v>
-      </c>
-      <c r="B360" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B360">
+        <v>2512000176</v>
       </c>
       <c r="C360" t="s">
         <v>12</v>
@@ -13318,13 +15641,22 @@
       <c r="K360" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L360" t="s">
+        <v>106</v>
+      </c>
+      <c r="M360" t="s">
+        <v>106</v>
+      </c>
+      <c r="N360" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>106</v>
-      </c>
-      <c r="B361" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B361">
+        <v>2512000176</v>
       </c>
       <c r="C361" t="s">
         <v>12</v>
@@ -13353,13 +15685,22 @@
       <c r="K361" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L361" t="s">
+        <v>106</v>
+      </c>
+      <c r="M361" t="s">
+        <v>106</v>
+      </c>
+      <c r="N361" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>106</v>
-      </c>
-      <c r="B362" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B362">
+        <v>2512000176</v>
       </c>
       <c r="C362" t="s">
         <v>12</v>
@@ -13388,13 +15729,19 @@
       <c r="K362" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L362" t="s">
+        <v>106</v>
+      </c>
+      <c r="M362" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>106</v>
-      </c>
-      <c r="B363" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B363">
+        <v>2512000176</v>
       </c>
       <c r="C363" t="s">
         <v>12</v>
@@ -13423,16 +15770,22 @@
       <c r="K363" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L363" t="s">
+        <v>106</v>
+      </c>
+      <c r="M363" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>106</v>
-      </c>
-      <c r="B364" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B364">
+        <v>2512000176</v>
       </c>
       <c r="C364" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D364">
         <v>0</v>
@@ -13458,13 +15811,19 @@
       <c r="K364" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L364" t="s">
+        <v>106</v>
+      </c>
+      <c r="M364" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>106</v>
-      </c>
-      <c r="B365" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B365">
+        <v>2512000176</v>
       </c>
       <c r="C365" t="s">
         <v>12</v>
@@ -13493,13 +15852,19 @@
       <c r="K365" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L365" t="s">
+        <v>106</v>
+      </c>
+      <c r="M365" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>106</v>
-      </c>
-      <c r="B366" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B366">
+        <v>2512000176</v>
       </c>
       <c r="C366" t="s">
         <v>37</v>
@@ -13528,13 +15893,19 @@
       <c r="K366" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L366" t="s">
+        <v>106</v>
+      </c>
+      <c r="M366" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>106</v>
-      </c>
-      <c r="B367" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B367">
+        <v>2512000176</v>
       </c>
       <c r="C367" t="s">
         <v>56</v>
@@ -13563,13 +15934,19 @@
       <c r="K367" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L367" t="s">
+        <v>106</v>
+      </c>
+      <c r="M367" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>106</v>
-      </c>
-      <c r="B368" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B368">
+        <v>2512000176</v>
       </c>
       <c r="C368" t="s">
         <v>12</v>
@@ -13598,13 +15975,22 @@
       <c r="K368" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L368" t="s">
+        <v>106</v>
+      </c>
+      <c r="M368" t="s">
+        <v>106</v>
+      </c>
+      <c r="N368" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>106</v>
-      </c>
-      <c r="B369" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B369">
+        <v>2512000176</v>
       </c>
       <c r="C369" t="s">
         <v>12</v>
@@ -13632,6 +16018,15 @@
       </c>
       <c r="K369" t="s">
         <v>18</v>
+      </c>
+      <c r="L369" t="s">
+        <v>106</v>
+      </c>
+      <c r="M369" t="s">
+        <v>106</v>
+      </c>
+      <c r="N369" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Deviation.xlsx
+++ b/Deviation.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4F5876-674E-4A2E-83A8-5A66E85AF2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2252E89B-2A2C-4A83-B555-F19FC9ADB651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$N$369</definedName>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3747" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3846" uniqueCount="115">
   <si>
     <t>District</t>
   </si>
@@ -345,28 +346,40 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>لياقت</t>
-  </si>
-  <si>
-    <t>محمد على</t>
-  </si>
-  <si>
-    <t>ياسر عبد الرحمن</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>طارق عمار</t>
+    <t>Total Deviation</t>
   </si>
   <si>
-    <t>اسلام عبد القوي</t>
+    <t>Tariq / Ammar</t>
   </si>
   <si>
-    <t>مقاول باطن / تابع لمهند</t>
+    <t>Liyaqt</t>
   </si>
   <si>
-    <t>مهند</t>
+    <t>Subcont. Related to Mohannad</t>
+  </si>
+  <si>
+    <t>Yasser Abdelrahaman</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Mohamed Ali</t>
+  </si>
+  <si>
+    <t>Muhannad</t>
+  </si>
+  <si>
+    <t>Islam Abdelkawi</t>
+  </si>
+  <si>
+    <t>Adel</t>
+  </si>
+  <si>
+    <t>Abu omar</t>
   </si>
 </sst>
 </file>
@@ -817,10 +830,10 @@
         <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -858,10 +871,10 @@
         <v>22</v>
       </c>
       <c r="L3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -899,10 +912,10 @@
         <v>22</v>
       </c>
       <c r="L4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -940,10 +953,10 @@
         <v>22</v>
       </c>
       <c r="L5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -981,10 +994,10 @@
         <v>22</v>
       </c>
       <c r="L6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1022,10 +1035,10 @@
         <v>22</v>
       </c>
       <c r="L7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M7" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1063,10 +1076,10 @@
         <v>22</v>
       </c>
       <c r="L8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M8" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1104,10 +1117,10 @@
         <v>22</v>
       </c>
       <c r="L9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M9" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1145,10 +1158,10 @@
         <v>22</v>
       </c>
       <c r="L10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M10" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1186,10 +1199,10 @@
         <v>22</v>
       </c>
       <c r="L11" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M11" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1227,10 +1240,10 @@
         <v>22</v>
       </c>
       <c r="L12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M12" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1268,10 +1281,10 @@
         <v>22</v>
       </c>
       <c r="L13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M13" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1309,10 +1322,10 @@
         <v>27</v>
       </c>
       <c r="L14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M14" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1350,10 +1363,10 @@
         <v>22</v>
       </c>
       <c r="L15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M15" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1391,10 +1404,10 @@
         <v>22</v>
       </c>
       <c r="L16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M16" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1432,10 +1445,10 @@
         <v>22</v>
       </c>
       <c r="L17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M17" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1473,10 +1486,10 @@
         <v>22</v>
       </c>
       <c r="L18" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1514,10 +1527,10 @@
         <v>22</v>
       </c>
       <c r="L19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M19" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1555,10 +1568,10 @@
         <v>18</v>
       </c>
       <c r="L20" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M20" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1596,10 +1609,10 @@
         <v>22</v>
       </c>
       <c r="L21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M21" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1637,10 +1650,10 @@
         <v>27</v>
       </c>
       <c r="L22" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M22" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1678,10 +1691,10 @@
         <v>27</v>
       </c>
       <c r="L23" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M23" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1719,10 +1732,10 @@
         <v>22</v>
       </c>
       <c r="L24" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M24" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1760,10 +1773,10 @@
         <v>27</v>
       </c>
       <c r="L25" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M25" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -1801,10 +1814,10 @@
         <v>22</v>
       </c>
       <c r="L26" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M26" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>102</v>
@@ -1845,10 +1858,10 @@
         <v>22</v>
       </c>
       <c r="L27" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M27" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>102</v>
@@ -1889,10 +1902,10 @@
         <v>22</v>
       </c>
       <c r="L28" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M28" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -1930,10 +1943,10 @@
         <v>22</v>
       </c>
       <c r="L29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M29" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -1971,10 +1984,10 @@
         <v>22</v>
       </c>
       <c r="L30" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M30" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2012,10 +2025,13 @@
         <v>22</v>
       </c>
       <c r="L31" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M31" t="s">
-        <v>104</v>
+        <v>110</v>
+      </c>
+      <c r="N31" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2053,13 +2069,13 @@
         <v>22</v>
       </c>
       <c r="L32" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M32" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>73</v>
       </c>
@@ -2094,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="L33" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M33" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>73</v>
       </c>
@@ -2135,13 +2151,13 @@
         <v>22</v>
       </c>
       <c r="L34" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M34" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -2176,13 +2192,13 @@
         <v>22</v>
       </c>
       <c r="L35" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M35" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -2217,13 +2233,13 @@
         <v>22</v>
       </c>
       <c r="L36" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M36" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -2258,13 +2274,13 @@
         <v>22</v>
       </c>
       <c r="L37" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M37" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>73</v>
       </c>
@@ -2299,13 +2315,16 @@
         <v>22</v>
       </c>
       <c r="L38" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M38" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N38" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>73</v>
       </c>
@@ -2340,13 +2359,13 @@
         <v>22</v>
       </c>
       <c r="L39" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M39" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>73</v>
       </c>
@@ -2381,13 +2400,13 @@
         <v>22</v>
       </c>
       <c r="L40" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>73</v>
       </c>
@@ -2422,13 +2441,13 @@
         <v>18</v>
       </c>
       <c r="L41" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M41" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>73</v>
       </c>
@@ -2463,13 +2482,16 @@
         <v>22</v>
       </c>
       <c r="L42" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M42" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N42" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>73</v>
       </c>
@@ -2504,13 +2526,13 @@
         <v>22</v>
       </c>
       <c r="L43" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M43" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>73</v>
       </c>
@@ -2545,13 +2567,13 @@
         <v>70</v>
       </c>
       <c r="L44" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M44" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -2586,13 +2608,13 @@
         <v>22</v>
       </c>
       <c r="L45" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M45" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>73</v>
       </c>
@@ -2627,13 +2649,13 @@
         <v>22</v>
       </c>
       <c r="L46" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M46" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>73</v>
       </c>
@@ -2668,13 +2690,13 @@
         <v>27</v>
       </c>
       <c r="L47" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M47" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>73</v>
       </c>
@@ -2709,13 +2731,13 @@
         <v>27</v>
       </c>
       <c r="L48" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M48" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>73</v>
       </c>
@@ -2750,13 +2772,13 @@
         <v>22</v>
       </c>
       <c r="L49" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M49" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>73</v>
       </c>
@@ -2791,13 +2813,13 @@
         <v>22</v>
       </c>
       <c r="L50" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M50" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>73</v>
       </c>
@@ -2832,13 +2854,13 @@
         <v>70</v>
       </c>
       <c r="L51" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M51" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>73</v>
       </c>
@@ -2873,13 +2895,13 @@
         <v>22</v>
       </c>
       <c r="L52" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M52" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -2914,13 +2936,13 @@
         <v>22</v>
       </c>
       <c r="L53" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M53" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>73</v>
       </c>
@@ -2955,13 +2977,16 @@
         <v>22</v>
       </c>
       <c r="L54" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M54" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N54" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>73</v>
       </c>
@@ -2996,13 +3021,13 @@
         <v>22</v>
       </c>
       <c r="L55" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M55" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>73</v>
       </c>
@@ -3037,13 +3062,13 @@
         <v>22</v>
       </c>
       <c r="L56" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M56" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>73</v>
       </c>
@@ -3078,13 +3103,13 @@
         <v>22</v>
       </c>
       <c r="L57" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M57" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>73</v>
       </c>
@@ -3119,13 +3144,13 @@
         <v>70</v>
       </c>
       <c r="L58" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M58" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>73</v>
       </c>
@@ -3160,13 +3185,13 @@
         <v>22</v>
       </c>
       <c r="L59" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M59" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>73</v>
       </c>
@@ -3201,13 +3226,13 @@
         <v>22</v>
       </c>
       <c r="L60" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M60" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>73</v>
       </c>
@@ -3242,13 +3267,13 @@
         <v>22</v>
       </c>
       <c r="L61" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M61" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>73</v>
       </c>
@@ -3283,13 +3308,13 @@
         <v>22</v>
       </c>
       <c r="L62" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M62" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>73</v>
       </c>
@@ -3324,13 +3349,13 @@
         <v>27</v>
       </c>
       <c r="L63" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M63" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>73</v>
       </c>
@@ -3365,13 +3390,13 @@
         <v>22</v>
       </c>
       <c r="L64" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M64" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -3406,13 +3431,13 @@
         <v>22</v>
       </c>
       <c r="L65" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M65" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>73</v>
       </c>
@@ -3447,13 +3472,13 @@
         <v>22</v>
       </c>
       <c r="L66" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M66" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>73</v>
       </c>
@@ -3488,13 +3513,13 @@
         <v>22</v>
       </c>
       <c r="L67" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M67" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>73</v>
       </c>
@@ -3529,13 +3554,13 @@
         <v>22</v>
       </c>
       <c r="L68" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M68" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -3570,13 +3595,13 @@
         <v>27</v>
       </c>
       <c r="L69" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M69" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -3611,13 +3636,13 @@
         <v>22</v>
       </c>
       <c r="L70" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M70" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -3652,13 +3677,13 @@
         <v>22</v>
       </c>
       <c r="L71" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M71" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -3693,13 +3718,13 @@
         <v>22</v>
       </c>
       <c r="L72" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M72" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -3734,13 +3759,13 @@
         <v>22</v>
       </c>
       <c r="L73" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M73" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -3775,13 +3800,13 @@
         <v>22</v>
       </c>
       <c r="L74" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M74" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>73</v>
       </c>
@@ -3816,13 +3841,13 @@
         <v>22</v>
       </c>
       <c r="L75" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M75" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>73</v>
       </c>
@@ -3857,13 +3882,13 @@
         <v>22</v>
       </c>
       <c r="L76" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M76" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>73</v>
       </c>
@@ -3898,13 +3923,13 @@
         <v>22</v>
       </c>
       <c r="L77" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M77" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>73</v>
       </c>
@@ -3939,13 +3964,16 @@
         <v>18</v>
       </c>
       <c r="L78" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M78" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N78" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>73</v>
       </c>
@@ -3980,13 +4008,16 @@
         <v>22</v>
       </c>
       <c r="L79" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M79" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N79" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>73</v>
       </c>
@@ -4021,13 +4052,16 @@
         <v>22</v>
       </c>
       <c r="L80" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M80" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N80" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>73</v>
       </c>
@@ -4062,13 +4096,16 @@
         <v>22</v>
       </c>
       <c r="L81" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M81" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N81" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>73</v>
       </c>
@@ -4103,13 +4140,13 @@
         <v>22</v>
       </c>
       <c r="L82" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M82" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>73</v>
       </c>
@@ -4144,13 +4181,13 @@
         <v>22</v>
       </c>
       <c r="L83" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M83" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>73</v>
       </c>
@@ -4185,13 +4222,13 @@
         <v>22</v>
       </c>
       <c r="L84" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M84" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>73</v>
       </c>
@@ -4226,13 +4263,13 @@
         <v>22</v>
       </c>
       <c r="L85" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M85" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>73</v>
       </c>
@@ -4267,13 +4304,13 @@
         <v>22</v>
       </c>
       <c r="L86" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M86" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>73</v>
       </c>
@@ -4308,13 +4345,13 @@
         <v>22</v>
       </c>
       <c r="L87" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M87" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>73</v>
       </c>
@@ -4349,13 +4386,13 @@
         <v>22</v>
       </c>
       <c r="L88" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M88" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>73</v>
       </c>
@@ -4390,13 +4427,13 @@
         <v>70</v>
       </c>
       <c r="L89" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M89" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>73</v>
       </c>
@@ -4431,13 +4468,16 @@
         <v>18</v>
       </c>
       <c r="L90" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M90" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N90" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>73</v>
       </c>
@@ -4472,13 +4512,13 @@
         <v>22</v>
       </c>
       <c r="L91" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M91" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>73</v>
       </c>
@@ -4513,13 +4553,16 @@
         <v>22</v>
       </c>
       <c r="L92" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M92" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N92" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>73</v>
       </c>
@@ -4554,13 +4597,13 @@
         <v>22</v>
       </c>
       <c r="L93" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M93" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>73</v>
       </c>
@@ -4595,13 +4638,13 @@
         <v>22</v>
       </c>
       <c r="L94" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M94" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>73</v>
       </c>
@@ -4636,13 +4679,13 @@
         <v>22</v>
       </c>
       <c r="L95" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M95" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>73</v>
       </c>
@@ -4677,13 +4720,16 @@
         <v>18</v>
       </c>
       <c r="L96" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M96" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N96" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>73</v>
       </c>
@@ -4718,13 +4764,13 @@
         <v>22</v>
       </c>
       <c r="L97" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M97" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>73</v>
       </c>
@@ -4759,13 +4805,16 @@
         <v>18</v>
       </c>
       <c r="L98" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M98" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N98" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>73</v>
       </c>
@@ -4800,13 +4849,16 @@
         <v>18</v>
       </c>
       <c r="L99" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M99" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N99" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>73</v>
       </c>
@@ -4841,13 +4893,16 @@
         <v>22</v>
       </c>
       <c r="L100" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M100" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N100" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>73</v>
       </c>
@@ -4882,13 +4937,16 @@
         <v>18</v>
       </c>
       <c r="L101" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M101" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N101" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>73</v>
       </c>
@@ -4923,13 +4981,13 @@
         <v>70</v>
       </c>
       <c r="L102" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M102" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>73</v>
       </c>
@@ -4964,13 +5022,13 @@
         <v>22</v>
       </c>
       <c r="L103" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M103" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>73</v>
       </c>
@@ -5005,13 +5063,13 @@
         <v>22</v>
       </c>
       <c r="L104" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M104" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>73</v>
       </c>
@@ -5046,13 +5104,13 @@
         <v>22</v>
       </c>
       <c r="L105" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M105" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>73</v>
       </c>
@@ -5087,13 +5145,13 @@
         <v>22</v>
       </c>
       <c r="L106" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M106" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>73</v>
       </c>
@@ -5128,13 +5186,16 @@
         <v>22</v>
       </c>
       <c r="L107" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M107" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N107" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>73</v>
       </c>
@@ -5169,13 +5230,13 @@
         <v>22</v>
       </c>
       <c r="L108" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M108" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>73</v>
       </c>
@@ -5210,13 +5271,16 @@
         <v>18</v>
       </c>
       <c r="L109" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M109" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N109" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>73</v>
       </c>
@@ -5251,13 +5315,13 @@
         <v>22</v>
       </c>
       <c r="L110" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M110" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>73</v>
       </c>
@@ -5292,13 +5356,13 @@
         <v>22</v>
       </c>
       <c r="L111" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M111" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>73</v>
       </c>
@@ -5333,13 +5397,13 @@
         <v>27</v>
       </c>
       <c r="L112" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M112" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>73</v>
       </c>
@@ -5374,13 +5438,16 @@
         <v>18</v>
       </c>
       <c r="L113" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M113" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N113" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>73</v>
       </c>
@@ -5415,13 +5482,16 @@
         <v>18</v>
       </c>
       <c r="L114" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M114" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N114" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>73</v>
       </c>
@@ -5456,13 +5526,13 @@
         <v>22</v>
       </c>
       <c r="L115" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M115" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>73</v>
       </c>
@@ -5497,13 +5567,13 @@
         <v>22</v>
       </c>
       <c r="L116" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M116" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>73</v>
       </c>
@@ -5538,13 +5608,13 @@
         <v>22</v>
       </c>
       <c r="L117" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M117" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>73</v>
       </c>
@@ -5579,13 +5649,16 @@
         <v>18</v>
       </c>
       <c r="L118" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M118" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N118" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>73</v>
       </c>
@@ -5620,13 +5693,13 @@
         <v>22</v>
       </c>
       <c r="L119" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M119" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>73</v>
       </c>
@@ -5661,13 +5734,13 @@
         <v>22</v>
       </c>
       <c r="L120" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M120" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>73</v>
       </c>
@@ -5702,13 +5775,13 @@
         <v>22</v>
       </c>
       <c r="L121" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M121" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>73</v>
       </c>
@@ -5743,13 +5816,13 @@
         <v>22</v>
       </c>
       <c r="L122" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M122" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>73</v>
       </c>
@@ -5784,13 +5857,13 @@
         <v>22</v>
       </c>
       <c r="L123" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M123" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>73</v>
       </c>
@@ -5825,13 +5898,16 @@
         <v>18</v>
       </c>
       <c r="L124" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M124" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N124" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>73</v>
       </c>
@@ -5866,13 +5942,13 @@
         <v>22</v>
       </c>
       <c r="L125" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M125" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>73</v>
       </c>
@@ -5907,13 +5983,13 @@
         <v>22</v>
       </c>
       <c r="L126" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M126" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>73</v>
       </c>
@@ -5948,13 +6024,13 @@
         <v>22</v>
       </c>
       <c r="L127" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M127" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>73</v>
       </c>
@@ -5989,10 +6065,10 @@
         <v>22</v>
       </c>
       <c r="L128" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M128" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.3">
@@ -6030,10 +6106,10 @@
         <v>22</v>
       </c>
       <c r="L129" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M129" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.3">
@@ -6071,10 +6147,10 @@
         <v>22</v>
       </c>
       <c r="L130" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M130" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.3">
@@ -6112,10 +6188,10 @@
         <v>22</v>
       </c>
       <c r="L131" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M131" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.3">
@@ -6153,10 +6229,10 @@
         <v>22</v>
       </c>
       <c r="L132" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M132" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.3">
@@ -6194,10 +6270,10 @@
         <v>22</v>
       </c>
       <c r="L133" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M133" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.3">
@@ -6235,10 +6311,10 @@
         <v>22</v>
       </c>
       <c r="L134" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M134" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.3">
@@ -6276,10 +6352,10 @@
         <v>22</v>
       </c>
       <c r="L135" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M135" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.3">
@@ -6317,10 +6393,10 @@
         <v>22</v>
       </c>
       <c r="L136" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M136" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.3">
@@ -6358,10 +6434,10 @@
         <v>22</v>
       </c>
       <c r="L137" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M137" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.3">
@@ -6399,10 +6475,10 @@
         <v>22</v>
       </c>
       <c r="L138" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M138" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.3">
@@ -6440,10 +6516,10 @@
         <v>22</v>
       </c>
       <c r="L139" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M139" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.3">
@@ -6481,10 +6557,10 @@
         <v>22</v>
       </c>
       <c r="L140" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M140" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.3">
@@ -6522,10 +6598,10 @@
         <v>22</v>
       </c>
       <c r="L141" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M141" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.3">
@@ -6563,10 +6639,10 @@
         <v>22</v>
       </c>
       <c r="L142" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M142" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.3">
@@ -6604,10 +6680,10 @@
         <v>22</v>
       </c>
       <c r="L143" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M143" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.3">
@@ -6645,13 +6721,13 @@
         <v>22</v>
       </c>
       <c r="L144" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M144" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>73</v>
       </c>
@@ -6686,13 +6762,13 @@
         <v>22</v>
       </c>
       <c r="L145" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M145" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>73</v>
       </c>
@@ -6727,13 +6803,13 @@
         <v>22</v>
       </c>
       <c r="L146" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M146" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>73</v>
       </c>
@@ -6768,13 +6844,13 @@
         <v>22</v>
       </c>
       <c r="L147" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M147" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>73</v>
       </c>
@@ -6809,13 +6885,13 @@
         <v>22</v>
       </c>
       <c r="L148" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M148" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>73</v>
       </c>
@@ -6850,13 +6926,13 @@
         <v>22</v>
       </c>
       <c r="L149" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M149" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>73</v>
       </c>
@@ -6891,13 +6967,13 @@
         <v>27</v>
       </c>
       <c r="L150" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M150" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>73</v>
       </c>
@@ -6932,13 +7008,13 @@
         <v>22</v>
       </c>
       <c r="L151" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M151" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>73</v>
       </c>
@@ -6973,13 +7049,13 @@
         <v>22</v>
       </c>
       <c r="L152" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M152" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>73</v>
       </c>
@@ -7014,13 +7090,13 @@
         <v>22</v>
       </c>
       <c r="L153" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M153" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>73</v>
       </c>
@@ -7055,13 +7131,16 @@
         <v>22</v>
       </c>
       <c r="L154" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M154" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="N154" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>73</v>
       </c>
@@ -7096,13 +7175,13 @@
         <v>27</v>
       </c>
       <c r="L155" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M155" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>73</v>
       </c>
@@ -7137,13 +7216,13 @@
         <v>70</v>
       </c>
       <c r="L156" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M156" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>73</v>
       </c>
@@ -7178,13 +7257,13 @@
         <v>22</v>
       </c>
       <c r="L157" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M157" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>73</v>
       </c>
@@ -7219,13 +7298,13 @@
         <v>27</v>
       </c>
       <c r="L158" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M158" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>73</v>
       </c>
@@ -7260,13 +7339,13 @@
         <v>27</v>
       </c>
       <c r="L159" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M159" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>73</v>
       </c>
@@ -7301,10 +7380,10 @@
         <v>22</v>
       </c>
       <c r="L160" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M160" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.3">
@@ -7342,10 +7421,10 @@
         <v>22</v>
       </c>
       <c r="L161" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M161" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.3">
@@ -7383,10 +7462,10 @@
         <v>22</v>
       </c>
       <c r="L162" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M162" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.3">
@@ -7424,10 +7503,10 @@
         <v>22</v>
       </c>
       <c r="L163" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M163" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.3">
@@ -7465,10 +7544,10 @@
         <v>22</v>
       </c>
       <c r="L164" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M164" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.3">
@@ -7506,10 +7585,10 @@
         <v>27</v>
       </c>
       <c r="L165" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M165" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.3">
@@ -7547,10 +7626,10 @@
         <v>22</v>
       </c>
       <c r="L166" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M166" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.3">
@@ -7588,10 +7667,10 @@
         <v>22</v>
       </c>
       <c r="L167" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M167" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.3">
@@ -7629,10 +7708,10 @@
         <v>22</v>
       </c>
       <c r="L168" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M168" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.3">
@@ -7670,10 +7749,10 @@
         <v>22</v>
       </c>
       <c r="L169" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M169" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.3">
@@ -7711,10 +7790,10 @@
         <v>22</v>
       </c>
       <c r="L170" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M170" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.3">
@@ -7752,10 +7831,10 @@
         <v>22</v>
       </c>
       <c r="L171" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M171" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.3">
@@ -7793,10 +7872,10 @@
         <v>22</v>
       </c>
       <c r="L172" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M172" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.3">
@@ -7834,10 +7913,10 @@
         <v>22</v>
       </c>
       <c r="L173" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M173" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.3">
@@ -7875,10 +7954,10 @@
         <v>22</v>
       </c>
       <c r="L174" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M174" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.3">
@@ -7916,10 +7995,10 @@
         <v>22</v>
       </c>
       <c r="L175" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M175" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.3">
@@ -7957,13 +8036,13 @@
         <v>22</v>
       </c>
       <c r="L176" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M176" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>73</v>
       </c>
@@ -7998,13 +8077,13 @@
         <v>27</v>
       </c>
       <c r="L177" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M177" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>73</v>
       </c>
@@ -8039,13 +8118,13 @@
         <v>22</v>
       </c>
       <c r="L178" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M178" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>73</v>
       </c>
@@ -8080,13 +8159,13 @@
         <v>22</v>
       </c>
       <c r="L179" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M179" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>73</v>
       </c>
@@ -8121,13 +8200,13 @@
         <v>27</v>
       </c>
       <c r="L180" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M180" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>73</v>
       </c>
@@ -8162,13 +8241,13 @@
         <v>22</v>
       </c>
       <c r="L181" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M181" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>73</v>
       </c>
@@ -8203,13 +8282,13 @@
         <v>22</v>
       </c>
       <c r="L182" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M182" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>73</v>
       </c>
@@ -8244,13 +8323,13 @@
         <v>22</v>
       </c>
       <c r="L183" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M183" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>73</v>
       </c>
@@ -8285,13 +8364,13 @@
         <v>27</v>
       </c>
       <c r="L184" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M184" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>73</v>
       </c>
@@ -8326,13 +8405,13 @@
         <v>27</v>
       </c>
       <c r="L185" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M185" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>73</v>
       </c>
@@ -8367,13 +8446,16 @@
         <v>18</v>
       </c>
       <c r="L186" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M186" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="N186" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>73</v>
       </c>
@@ -8408,13 +8490,16 @@
         <v>18</v>
       </c>
       <c r="L187" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M187" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="N187" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>73</v>
       </c>
@@ -8449,13 +8534,16 @@
         <v>70</v>
       </c>
       <c r="L188" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M188" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="N188" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>73</v>
       </c>
@@ -8490,13 +8578,13 @@
         <v>27</v>
       </c>
       <c r="L189" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M189" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>73</v>
       </c>
@@ -8531,13 +8619,13 @@
         <v>27</v>
       </c>
       <c r="L190" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M190" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>73</v>
       </c>
@@ -8572,13 +8660,13 @@
         <v>22</v>
       </c>
       <c r="L191" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M191" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>73</v>
       </c>
@@ -8613,13 +8701,13 @@
         <v>22</v>
       </c>
       <c r="L192" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M192" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>73</v>
       </c>
@@ -8654,13 +8742,13 @@
         <v>22</v>
       </c>
       <c r="L193" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M193" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>73</v>
       </c>
@@ -8695,13 +8783,13 @@
         <v>22</v>
       </c>
       <c r="L194" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M194" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>73</v>
       </c>
@@ -8736,13 +8824,13 @@
         <v>22</v>
       </c>
       <c r="L195" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M195" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>73</v>
       </c>
@@ -8777,13 +8865,13 @@
         <v>22</v>
       </c>
       <c r="L196" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M196" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>73</v>
       </c>
@@ -8818,13 +8906,13 @@
         <v>22</v>
       </c>
       <c r="L197" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M197" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>73</v>
       </c>
@@ -8859,13 +8947,13 @@
         <v>22</v>
       </c>
       <c r="L198" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M198" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>73</v>
       </c>
@@ -8900,13 +8988,13 @@
         <v>22</v>
       </c>
       <c r="L199" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M199" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>73</v>
       </c>
@@ -8941,13 +9029,13 @@
         <v>22</v>
       </c>
       <c r="L200" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M200" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>73</v>
       </c>
@@ -8982,13 +9070,13 @@
         <v>22</v>
       </c>
       <c r="L201" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M201" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>73</v>
       </c>
@@ -9023,13 +9111,13 @@
         <v>22</v>
       </c>
       <c r="L202" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M202" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>73</v>
       </c>
@@ -9064,13 +9152,13 @@
         <v>18</v>
       </c>
       <c r="L203" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M203" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>73</v>
       </c>
@@ -9105,13 +9193,16 @@
         <v>70</v>
       </c>
       <c r="L204" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M204" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+      <c r="N204" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>73</v>
       </c>
@@ -9146,13 +9237,13 @@
         <v>70</v>
       </c>
       <c r="L205" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M205" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>73</v>
       </c>
@@ -9187,13 +9278,13 @@
         <v>27</v>
       </c>
       <c r="L206" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M206" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>73</v>
       </c>
@@ -9228,13 +9319,13 @@
         <v>22</v>
       </c>
       <c r="L207" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M207" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>73</v>
       </c>
@@ -9269,13 +9360,13 @@
         <v>22</v>
       </c>
       <c r="L208" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M208" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>73</v>
       </c>
@@ -9310,13 +9401,13 @@
         <v>22</v>
       </c>
       <c r="L209" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M209" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>73</v>
       </c>
@@ -9351,13 +9442,13 @@
         <v>22</v>
       </c>
       <c r="L210" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M210" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>73</v>
       </c>
@@ -9392,13 +9483,13 @@
         <v>22</v>
       </c>
       <c r="L211" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M211" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>73</v>
       </c>
@@ -9433,13 +9524,13 @@
         <v>22</v>
       </c>
       <c r="L212" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M212" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>73</v>
       </c>
@@ -9474,13 +9565,13 @@
         <v>22</v>
       </c>
       <c r="L213" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M213" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>73</v>
       </c>
@@ -9515,13 +9606,13 @@
         <v>22</v>
       </c>
       <c r="L214" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M214" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>73</v>
       </c>
@@ -9556,13 +9647,13 @@
         <v>22</v>
       </c>
       <c r="L215" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M215" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>73</v>
       </c>
@@ -9597,13 +9688,13 @@
         <v>22</v>
       </c>
       <c r="L216" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M216" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>73</v>
       </c>
@@ -9638,13 +9729,13 @@
         <v>22</v>
       </c>
       <c r="L217" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M217" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>73</v>
       </c>
@@ -9679,13 +9770,13 @@
         <v>18</v>
       </c>
       <c r="L218" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="M218" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>98</v>
       </c>
@@ -9720,13 +9811,16 @@
         <v>22</v>
       </c>
       <c r="L219" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M219" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="N219" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>98</v>
       </c>
@@ -9761,13 +9855,16 @@
         <v>22</v>
       </c>
       <c r="L220" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M220" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="N220" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>98</v>
       </c>
@@ -9802,13 +9899,16 @@
         <v>22</v>
       </c>
       <c r="L221" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M221" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="N221" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -9843,13 +9943,16 @@
         <v>22</v>
       </c>
       <c r="L222" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M222" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="N222" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>98</v>
       </c>
@@ -9884,13 +9987,13 @@
         <v>22</v>
       </c>
       <c r="L223" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M223" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>98</v>
       </c>
@@ -9925,13 +10028,13 @@
         <v>22</v>
       </c>
       <c r="L224" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M224" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>98</v>
       </c>
@@ -9966,13 +10069,13 @@
         <v>22</v>
       </c>
       <c r="L225" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M225" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>98</v>
       </c>
@@ -10007,13 +10110,13 @@
         <v>22</v>
       </c>
       <c r="L226" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M226" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>98</v>
       </c>
@@ -10048,13 +10151,13 @@
         <v>18</v>
       </c>
       <c r="L227" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M227" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>98</v>
       </c>
@@ -10089,13 +10192,13 @@
         <v>22</v>
       </c>
       <c r="L228" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M228" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>98</v>
       </c>
@@ -10130,13 +10233,13 @@
         <v>22</v>
       </c>
       <c r="L229" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M229" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>98</v>
       </c>
@@ -10171,13 +10274,13 @@
         <v>22</v>
       </c>
       <c r="L230" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M230" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>98</v>
       </c>
@@ -10212,13 +10315,13 @@
         <v>22</v>
       </c>
       <c r="L231" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M231" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>98</v>
       </c>
@@ -10253,13 +10356,13 @@
         <v>22</v>
       </c>
       <c r="L232" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M232" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>98</v>
       </c>
@@ -10294,13 +10397,13 @@
         <v>27</v>
       </c>
       <c r="L233" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M233" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>98</v>
       </c>
@@ -10335,13 +10438,13 @@
         <v>22</v>
       </c>
       <c r="L234" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M234" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>98</v>
       </c>
@@ -10376,13 +10479,16 @@
         <v>22</v>
       </c>
       <c r="L235" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M235" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="N235" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>98</v>
       </c>
@@ -10417,13 +10523,16 @@
         <v>22</v>
       </c>
       <c r="L236" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M236" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="N236" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>98</v>
       </c>
@@ -10458,13 +10567,16 @@
         <v>22</v>
       </c>
       <c r="L237" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M237" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="N237" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>98</v>
       </c>
@@ -10499,13 +10611,13 @@
         <v>22</v>
       </c>
       <c r="L238" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M238" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>98</v>
       </c>
@@ -10540,13 +10652,13 @@
         <v>22</v>
       </c>
       <c r="L239" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M239" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>98</v>
       </c>
@@ -10581,10 +10693,10 @@
         <v>22</v>
       </c>
       <c r="L240" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M240" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.3">
@@ -10622,10 +10734,10 @@
         <v>22</v>
       </c>
       <c r="L241" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M241" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.3">
@@ -10663,10 +10775,10 @@
         <v>18</v>
       </c>
       <c r="L242" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M242" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.3">
@@ -10704,10 +10816,10 @@
         <v>22</v>
       </c>
       <c r="L243" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M243" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.3">
@@ -10745,10 +10857,10 @@
         <v>22</v>
       </c>
       <c r="L244" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M244" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.3">
@@ -10786,10 +10898,10 @@
         <v>22</v>
       </c>
       <c r="L245" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M245" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.3">
@@ -10827,10 +10939,10 @@
         <v>22</v>
       </c>
       <c r="L246" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M246" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.3">
@@ -10868,10 +10980,10 @@
         <v>22</v>
       </c>
       <c r="L247" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M247" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.3">
@@ -10909,10 +11021,10 @@
         <v>22</v>
       </c>
       <c r="L248" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M248" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.3">
@@ -10950,10 +11062,10 @@
         <v>22</v>
       </c>
       <c r="L249" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M249" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.3">
@@ -10991,10 +11103,10 @@
         <v>18</v>
       </c>
       <c r="L250" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M250" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.3">
@@ -11032,10 +11144,10 @@
         <v>22</v>
       </c>
       <c r="L251" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M251" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.3">
@@ -11073,10 +11185,10 @@
         <v>22</v>
       </c>
       <c r="L252" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M252" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.3">
@@ -11114,10 +11226,10 @@
         <v>22</v>
       </c>
       <c r="L253" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M253" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.3">
@@ -11155,10 +11267,10 @@
         <v>22</v>
       </c>
       <c r="L254" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M254" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.3">
@@ -11196,10 +11308,10 @@
         <v>22</v>
       </c>
       <c r="L255" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M255" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="256" spans="1:13" x14ac:dyDescent="0.3">
@@ -11237,10 +11349,10 @@
         <v>22</v>
       </c>
       <c r="L256" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M256" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.3">
@@ -11278,10 +11390,10 @@
         <v>22</v>
       </c>
       <c r="L257" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M257" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.3">
@@ -11319,10 +11431,10 @@
         <v>22</v>
       </c>
       <c r="L258" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M258" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.3">
@@ -11360,10 +11472,10 @@
         <v>22</v>
       </c>
       <c r="L259" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M259" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.3">
@@ -11401,10 +11513,10 @@
         <v>22</v>
       </c>
       <c r="L260" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M260" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N260" s="2" t="s">
         <v>102</v>
@@ -11445,10 +11557,10 @@
         <v>22</v>
       </c>
       <c r="L261" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M261" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N261" s="2" t="s">
         <v>102</v>
@@ -11489,10 +11601,10 @@
         <v>22</v>
       </c>
       <c r="L262" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M262" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N262" s="2" t="s">
         <v>102</v>
@@ -11533,10 +11645,10 @@
         <v>22</v>
       </c>
       <c r="L263" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M263" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N263" s="2" t="s">
         <v>102</v>
@@ -11577,10 +11689,10 @@
         <v>22</v>
       </c>
       <c r="L264" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M264" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N264" s="2" t="s">
         <v>102</v>
@@ -11621,10 +11733,10 @@
         <v>22</v>
       </c>
       <c r="L265" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M265" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N265" s="2" t="s">
         <v>102</v>
@@ -11665,10 +11777,10 @@
         <v>22</v>
       </c>
       <c r="L266" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M266" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N266" s="2" t="s">
         <v>102</v>
@@ -11709,10 +11821,10 @@
         <v>22</v>
       </c>
       <c r="L267" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M267" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N267" s="2" t="s">
         <v>102</v>
@@ -11753,10 +11865,10 @@
         <v>22</v>
       </c>
       <c r="L268" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M268" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N268" s="2" t="s">
         <v>102</v>
@@ -11797,10 +11909,10 @@
         <v>22</v>
       </c>
       <c r="L269" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M269" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N269" s="2" t="s">
         <v>102</v>
@@ -11841,10 +11953,10 @@
         <v>22</v>
       </c>
       <c r="L270" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M270" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N270" s="2" t="s">
         <v>102</v>
@@ -11885,10 +11997,10 @@
         <v>22</v>
       </c>
       <c r="L271" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M271" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N271" s="2" t="s">
         <v>102</v>
@@ -11929,10 +12041,10 @@
         <v>27</v>
       </c>
       <c r="L272" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M272" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.3">
@@ -11970,10 +12082,10 @@
         <v>22</v>
       </c>
       <c r="L273" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M273" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.3">
@@ -12011,10 +12123,13 @@
         <v>22</v>
       </c>
       <c r="L274" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M274" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="N274" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.3">
@@ -12052,10 +12167,13 @@
         <v>22</v>
       </c>
       <c r="L275" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M275" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="N275" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.3">
@@ -12093,10 +12211,13 @@
         <v>22</v>
       </c>
       <c r="L276" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M276" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="N276" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.3">
@@ -12134,10 +12255,13 @@
         <v>22</v>
       </c>
       <c r="L277" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M277" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="N277" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.3">
@@ -12175,10 +12299,13 @@
         <v>22</v>
       </c>
       <c r="L278" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M278" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="N278" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.3">
@@ -12216,10 +12343,13 @@
         <v>22</v>
       </c>
       <c r="L279" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M279" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="N279" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.3">
@@ -12257,10 +12387,13 @@
         <v>22</v>
       </c>
       <c r="L280" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M280" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="N280" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.3">
@@ -12298,10 +12431,13 @@
         <v>22</v>
       </c>
       <c r="L281" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M281" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="N281" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.3">
@@ -12339,10 +12475,13 @@
         <v>22</v>
       </c>
       <c r="L282" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M282" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="N282" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.3">
@@ -12380,10 +12519,10 @@
         <v>18</v>
       </c>
       <c r="L283" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M283" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.3">
@@ -12421,10 +12560,10 @@
         <v>22</v>
       </c>
       <c r="L284" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M284" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N284" s="2" t="s">
         <v>102</v>
@@ -12465,10 +12604,10 @@
         <v>22</v>
       </c>
       <c r="L285" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M285" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N285" s="2" t="s">
         <v>102</v>
@@ -12509,10 +12648,10 @@
         <v>22</v>
       </c>
       <c r="L286" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M286" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N286" s="2" t="s">
         <v>102</v>
@@ -12553,10 +12692,10 @@
         <v>22</v>
       </c>
       <c r="L287" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M287" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N287" s="2" t="s">
         <v>102</v>
@@ -12597,10 +12736,10 @@
         <v>22</v>
       </c>
       <c r="L288" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M288" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N288" s="2" t="s">
         <v>102</v>
@@ -12641,10 +12780,10 @@
         <v>22</v>
       </c>
       <c r="L289" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M289" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N289" s="2" t="s">
         <v>102</v>
@@ -12685,10 +12824,10 @@
         <v>22</v>
       </c>
       <c r="L290" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M290" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.3">
@@ -12726,10 +12865,10 @@
         <v>22</v>
       </c>
       <c r="L291" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M291" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N291" s="2" t="s">
         <v>102</v>
@@ -12770,10 +12909,10 @@
         <v>22</v>
       </c>
       <c r="L292" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M292" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N292" s="2" t="s">
         <v>102</v>
@@ -12814,10 +12953,10 @@
         <v>22</v>
       </c>
       <c r="L293" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M293" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.3">
@@ -12855,10 +12994,10 @@
         <v>18</v>
       </c>
       <c r="L294" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M294" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.3">
@@ -12896,10 +13035,10 @@
         <v>22</v>
       </c>
       <c r="L295" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M295" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.3">
@@ -12937,10 +13076,10 @@
         <v>18</v>
       </c>
       <c r="L296" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M296" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N296" s="2" t="s">
         <v>102</v>
@@ -12981,10 +13120,10 @@
         <v>18</v>
       </c>
       <c r="L297" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M297" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N297" s="2" t="s">
         <v>102</v>
@@ -13025,10 +13164,10 @@
         <v>18</v>
       </c>
       <c r="L298" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M298" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.3">
@@ -13066,10 +13205,10 @@
         <v>22</v>
       </c>
       <c r="L299" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M299" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N299" s="2" t="s">
         <v>102</v>
@@ -13110,10 +13249,10 @@
         <v>22</v>
       </c>
       <c r="L300" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M300" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N300" s="2" t="s">
         <v>102</v>
@@ -13154,10 +13293,10 @@
         <v>22</v>
       </c>
       <c r="L301" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M301" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N301" s="2" t="s">
         <v>102</v>
@@ -13198,10 +13337,10 @@
         <v>22</v>
       </c>
       <c r="L302" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M302" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N302" s="2" t="s">
         <v>102</v>
@@ -13242,10 +13381,10 @@
         <v>22</v>
       </c>
       <c r="L303" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M303" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N303" s="2" t="s">
         <v>102</v>
@@ -13286,10 +13425,10 @@
         <v>22</v>
       </c>
       <c r="L304" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M304" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N304" s="2" t="s">
         <v>102</v>
@@ -13330,10 +13469,10 @@
         <v>22</v>
       </c>
       <c r="L305" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M305" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N305" s="2" t="s">
         <v>102</v>
@@ -13374,10 +13513,10 @@
         <v>22</v>
       </c>
       <c r="L306" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M306" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N306" s="2" t="s">
         <v>102</v>
@@ -13418,10 +13557,10 @@
         <v>22</v>
       </c>
       <c r="L307" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M307" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N307" s="2" t="s">
         <v>102</v>
@@ -13462,10 +13601,10 @@
         <v>22</v>
       </c>
       <c r="L308" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M308" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N308" s="2" t="s">
         <v>102</v>
@@ -13506,10 +13645,10 @@
         <v>22</v>
       </c>
       <c r="L309" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M309" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.3">
@@ -13547,10 +13686,10 @@
         <v>22</v>
       </c>
       <c r="L310" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M310" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.3">
@@ -13588,10 +13727,10 @@
         <v>18</v>
       </c>
       <c r="L311" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M311" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.3">
@@ -13629,10 +13768,10 @@
         <v>22</v>
       </c>
       <c r="L312" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M312" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.3">
@@ -13670,10 +13809,10 @@
         <v>22</v>
       </c>
       <c r="L313" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M313" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.3">
@@ -13711,10 +13850,10 @@
         <v>22</v>
       </c>
       <c r="L314" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M314" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.3">
@@ -13752,10 +13891,10 @@
         <v>22</v>
       </c>
       <c r="L315" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M315" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.3">
@@ -13793,10 +13932,13 @@
         <v>22</v>
       </c>
       <c r="L316" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M316" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="N316" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.3">
@@ -13834,10 +13976,10 @@
         <v>22</v>
       </c>
       <c r="L317" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M317" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.3">
@@ -13875,10 +14017,10 @@
         <v>22</v>
       </c>
       <c r="L318" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M318" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.3">
@@ -13916,10 +14058,10 @@
         <v>18</v>
       </c>
       <c r="L319" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M319" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N319" s="2" t="s">
         <v>102</v>
@@ -13960,10 +14102,10 @@
         <v>18</v>
       </c>
       <c r="L320" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M320" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N320" s="2" t="s">
         <v>102</v>
@@ -14004,10 +14146,10 @@
         <v>18</v>
       </c>
       <c r="L321" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M321" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N321" s="2" t="s">
         <v>102</v>
@@ -14048,10 +14190,13 @@
         <v>70</v>
       </c>
       <c r="L322" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M322" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="N322" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.3">
@@ -14089,10 +14234,10 @@
         <v>22</v>
       </c>
       <c r="L323" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M323" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N323" s="2" t="s">
         <v>102</v>
@@ -14133,10 +14278,10 @@
         <v>22</v>
       </c>
       <c r="L324" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M324" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N324" s="2" t="s">
         <v>102</v>
@@ -14177,10 +14322,10 @@
         <v>22</v>
       </c>
       <c r="L325" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M325" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N325" s="2" t="s">
         <v>102</v>
@@ -14221,10 +14366,10 @@
         <v>22</v>
       </c>
       <c r="L326" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M326" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N326" s="2" t="s">
         <v>102</v>
@@ -14265,10 +14410,10 @@
         <v>22</v>
       </c>
       <c r="L327" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M327" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N327" s="2" t="s">
         <v>102</v>
@@ -14309,10 +14454,10 @@
         <v>22</v>
       </c>
       <c r="L328" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M328" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N328" s="2" t="s">
         <v>102</v>
@@ -14353,10 +14498,10 @@
         <v>22</v>
       </c>
       <c r="L329" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M329" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N329" s="2" t="s">
         <v>102</v>
@@ -14397,10 +14542,10 @@
         <v>22</v>
       </c>
       <c r="L330" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M330" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N330" s="2" t="s">
         <v>102</v>
@@ -14441,10 +14586,10 @@
         <v>22</v>
       </c>
       <c r="L331" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M331" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N331" s="2" t="s">
         <v>102</v>
@@ -14485,10 +14630,10 @@
         <v>22</v>
       </c>
       <c r="L332" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M332" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N332" s="2" t="s">
         <v>102</v>
@@ -14529,10 +14674,10 @@
         <v>22</v>
       </c>
       <c r="L333" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M333" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N333" s="2" t="s">
         <v>102</v>
@@ -14573,10 +14718,10 @@
         <v>22</v>
       </c>
       <c r="L334" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M334" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N334" s="2" t="s">
         <v>102</v>
@@ -14617,10 +14762,13 @@
         <v>22</v>
       </c>
       <c r="L335" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M335" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="N335" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.3">
@@ -14658,13 +14806,13 @@
         <v>22</v>
       </c>
       <c r="L336" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M336" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>98</v>
       </c>
@@ -14699,13 +14847,13 @@
         <v>22</v>
       </c>
       <c r="L337" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M337" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>98</v>
       </c>
@@ -14740,13 +14888,13 @@
         <v>22</v>
       </c>
       <c r="L338" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M338" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>98</v>
       </c>
@@ -14781,13 +14929,13 @@
         <v>22</v>
       </c>
       <c r="L339" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M339" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>98</v>
       </c>
@@ -14822,13 +14970,13 @@
         <v>22</v>
       </c>
       <c r="L340" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M340" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>98</v>
       </c>
@@ -14863,13 +15011,13 @@
         <v>22</v>
       </c>
       <c r="L341" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M341" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>98</v>
       </c>
@@ -14904,13 +15052,13 @@
         <v>22</v>
       </c>
       <c r="L342" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M342" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>98</v>
       </c>
@@ -14945,13 +15093,13 @@
         <v>22</v>
       </c>
       <c r="L343" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M343" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>98</v>
       </c>
@@ -14986,13 +15134,13 @@
         <v>22</v>
       </c>
       <c r="L344" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M344" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>98</v>
       </c>
@@ -15027,13 +15175,13 @@
         <v>22</v>
       </c>
       <c r="L345" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M345" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>98</v>
       </c>
@@ -15068,13 +15216,13 @@
         <v>22</v>
       </c>
       <c r="L346" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M346" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>98</v>
       </c>
@@ -15109,13 +15257,13 @@
         <v>22</v>
       </c>
       <c r="L347" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M347" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>98</v>
       </c>
@@ -15150,13 +15298,13 @@
         <v>22</v>
       </c>
       <c r="L348" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M348" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>98</v>
       </c>
@@ -15191,13 +15339,13 @@
         <v>22</v>
       </c>
       <c r="L349" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M349" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>98</v>
       </c>
@@ -15232,13 +15380,13 @@
         <v>22</v>
       </c>
       <c r="L350" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M350" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>98</v>
       </c>
@@ -15273,13 +15421,16 @@
         <v>22</v>
       </c>
       <c r="L351" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M351" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="N351" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>98</v>
       </c>
@@ -15314,10 +15465,13 @@
         <v>22</v>
       </c>
       <c r="L352" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M352" t="s">
-        <v>106</v>
+        <v>109</v>
+      </c>
+      <c r="N352" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.3">
@@ -15355,10 +15509,10 @@
         <v>22</v>
       </c>
       <c r="L353" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M353" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.3">
@@ -15396,10 +15550,10 @@
         <v>22</v>
       </c>
       <c r="L354" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M354" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.3">
@@ -15437,10 +15591,10 @@
         <v>22</v>
       </c>
       <c r="L355" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M355" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.3">
@@ -15478,10 +15632,10 @@
         <v>22</v>
       </c>
       <c r="L356" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M356" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.3">
@@ -15519,10 +15673,10 @@
         <v>22</v>
       </c>
       <c r="L357" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M357" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.3">
@@ -15560,10 +15714,10 @@
         <v>22</v>
       </c>
       <c r="L358" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M358" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.3">
@@ -15601,10 +15755,10 @@
         <v>70</v>
       </c>
       <c r="L359" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M359" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.3">
@@ -15642,10 +15796,10 @@
         <v>18</v>
       </c>
       <c r="L360" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M360" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N360" s="2" t="s">
         <v>102</v>
@@ -15686,10 +15840,10 @@
         <v>18</v>
       </c>
       <c r="L361" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M361" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N361" s="2" t="s">
         <v>102</v>
@@ -15730,10 +15884,13 @@
         <v>18</v>
       </c>
       <c r="L362" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M362" t="s">
-        <v>106</v>
+        <v>109</v>
+      </c>
+      <c r="N362" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.3">
@@ -15771,10 +15928,13 @@
         <v>18</v>
       </c>
       <c r="L363" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M363" t="s">
-        <v>106</v>
+        <v>109</v>
+      </c>
+      <c r="N363" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.3">
@@ -15812,10 +15972,13 @@
         <v>18</v>
       </c>
       <c r="L364" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M364" t="s">
-        <v>106</v>
+        <v>109</v>
+      </c>
+      <c r="N364" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.3">
@@ -15853,10 +16016,13 @@
         <v>18</v>
       </c>
       <c r="L365" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M365" t="s">
-        <v>106</v>
+        <v>109</v>
+      </c>
+      <c r="N365" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.3">
@@ -15894,10 +16060,10 @@
         <v>22</v>
       </c>
       <c r="L366" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M366" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.3">
@@ -15935,10 +16101,10 @@
         <v>22</v>
       </c>
       <c r="L367" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M367" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.3">
@@ -15976,10 +16142,10 @@
         <v>18</v>
       </c>
       <c r="L368" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M368" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N368" s="2" t="s">
         <v>102</v>
@@ -16020,13 +16186,35 @@
         <v>18</v>
       </c>
       <c r="L369" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="M369" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N369" s="2" t="s">
         <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF1FA70-71D1-4CC3-988D-342FDA247E0A}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Deviation.xlsx
+++ b/Deviation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07339FEF-5E9B-4867-9BEB-43964AA6DED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF78BA68-593D-44F0-97E1-89548C5C7055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3811" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="124">
   <si>
     <t>District</t>
   </si>
@@ -398,6 +398,15 @@
   </si>
   <si>
     <t>% OF Total</t>
+  </si>
+  <si>
+    <t>Civil Deviation</t>
+  </si>
+  <si>
+    <t>Fiber Deviation</t>
+  </si>
+  <si>
+    <t>Safety Deviation</t>
   </si>
 </sst>
 </file>
@@ -16244,7 +16253,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF1FA70-71D1-4CC3-988D-342FDA247E0A}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
@@ -16252,15 +16261,18 @@
     <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" customWidth="1"/>
+    <col min="9" max="9" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.109375" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -16277,25 +16289,34 @@
         <v>116</v>
       </c>
       <c r="F1" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>2521001669</v>
       </c>
@@ -16312,21 +16333,30 @@
         <v>6</v>
       </c>
       <c r="F2" s="3">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G2" s="3">
+        <v>22</v>
+      </c>
+      <c r="H2" s="3">
+        <v>5</v>
+      </c>
+      <c r="I2" s="3">
         <v>2</v>
       </c>
-      <c r="H2" s="3">
+      <c r="J2" s="3">
+        <v>32</v>
+      </c>
+      <c r="K2" s="3">
         <v>19</v>
       </c>
-      <c r="I2" s="5">
+      <c r="L2" s="5">
         <v>0.20699999999999999</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>109</v>
       </c>
     </row>
